--- a/data/profile2.xlsx
+++ b/data/profile2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/94468aa6da851130/Desktop/reto/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="450" documentId="8_{1E7C5D3D-50BB-4B39-8D4F-14058A714382}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B256754B-E306-4224-80A8-E954E8B0AF1C}"/>
+  <xr:revisionPtr revIDLastSave="453" documentId="8_{1E7C5D3D-50BB-4B39-8D4F-14058A714382}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2F29445B-D1C3-4517-B1E0-4BE311ABE5A8}"/>
   <bookViews>
-    <workbookView xWindow="75" yWindow="465" windowWidth="13935" windowHeight="14235" xr2:uid="{298304A4-FB78-45B5-B8F6-A597285BA23E}"/>
+    <workbookView xWindow="2490" yWindow="6720" windowWidth="15450" windowHeight="8460" xr2:uid="{298304A4-FB78-45B5-B8F6-A597285BA23E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -3945,7 +3945,7 @@
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="29.625" customWidth="1"/>
-    <col min="3" max="17" width="9" hidden="1" customWidth="1"/>
+    <col min="3" max="17" width="9" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.4">

--- a/data/profile2.xlsx
+++ b/data/profile2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/94468aa6da851130/Desktop/reto/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="453" documentId="8_{1E7C5D3D-50BB-4B39-8D4F-14058A714382}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2F29445B-D1C3-4517-B1E0-4BE311ABE5A8}"/>
+  <xr:revisionPtr revIDLastSave="454" documentId="8_{1E7C5D3D-50BB-4B39-8D4F-14058A714382}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{57A3F383-8FCB-4CC5-8C11-BB6D819F97C1}"/>
   <bookViews>
-    <workbookView xWindow="2490" yWindow="6720" windowWidth="15450" windowHeight="8460" xr2:uid="{298304A4-FB78-45B5-B8F6-A597285BA23E}"/>
+    <workbookView minimized="1" xWindow="3510" yWindow="3510" windowWidth="17820" windowHeight="8460" xr2:uid="{298304A4-FB78-45B5-B8F6-A597285BA23E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1145,9 +1145,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>シャーロット・ローラ</t>
-  </si>
-  <si>
     <t>万国</t>
     <rPh sb="0" eb="2">
       <t>バンコク</t>
@@ -3578,6 +3575,10 @@
   </si>
   <si>
     <t>闇鍋、羊の丸焼き、強めバカルディ</t>
+  </si>
+  <si>
+    <t>シャーロット・ローラ</t>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -3642,6 +3643,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4001,7 +4006,7 @@
         <v>16</v>
       </c>
       <c r="R1" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.4">
@@ -4009,7 +4014,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -4039,7 +4044,7 @@
         <v>22</v>
       </c>
       <c r="R2" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.4">
@@ -4083,7 +4088,7 @@
         <v>28</v>
       </c>
       <c r="R3" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.4">
@@ -4115,7 +4120,7 @@
         <v>33</v>
       </c>
       <c r="R4" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.4">
@@ -4153,7 +4158,7 @@
         <v>21</v>
       </c>
       <c r="R5" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.4">
@@ -4173,7 +4178,7 @@
         <v>180</v>
       </c>
       <c r="F6" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="G6" t="s">
         <v>38</v>
@@ -4200,7 +4205,7 @@
         <v>42</v>
       </c>
       <c r="R6" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.4">
@@ -4232,7 +4237,7 @@
         <v>20</v>
       </c>
       <c r="R7" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.4">
@@ -4267,7 +4272,7 @@
         <v>27</v>
       </c>
       <c r="R8" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.4">
@@ -4296,7 +4301,7 @@
         <v>20</v>
       </c>
       <c r="R9" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.4">
@@ -4328,7 +4333,7 @@
         <v>20</v>
       </c>
       <c r="R10" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.4">
@@ -4360,7 +4365,7 @@
         <v>20</v>
       </c>
       <c r="R11" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.4">
@@ -4398,7 +4403,7 @@
         <v>27</v>
       </c>
       <c r="R12" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.4">
@@ -4436,7 +4441,7 @@
         <v>64</v>
       </c>
       <c r="R13" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.4">
@@ -4477,7 +4482,7 @@
         <v>40</v>
       </c>
       <c r="R14" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.4">
@@ -4509,7 +4514,7 @@
         <v>20</v>
       </c>
       <c r="R15" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.4">
@@ -4547,7 +4552,7 @@
         <v>63</v>
       </c>
       <c r="R16" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.4">
@@ -4579,7 +4584,7 @@
         <v>20</v>
       </c>
       <c r="R17" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.4">
@@ -4614,7 +4619,7 @@
         <v>63</v>
       </c>
       <c r="R18" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.4">
@@ -4646,7 +4651,7 @@
         <v>20</v>
       </c>
       <c r="R19" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.4">
@@ -4678,7 +4683,7 @@
         <v>20</v>
       </c>
       <c r="R20" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.4">
@@ -4710,7 +4715,7 @@
         <v>33</v>
       </c>
       <c r="R21" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.4">
@@ -4745,7 +4750,7 @@
         <v>21</v>
       </c>
       <c r="R22" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.4">
@@ -4780,7 +4785,7 @@
         <v>63</v>
       </c>
       <c r="R23" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.4">
@@ -4815,7 +4820,7 @@
         <v>21</v>
       </c>
       <c r="R24" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.4">
@@ -4850,7 +4855,7 @@
         <v>80</v>
       </c>
       <c r="R25" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.4">
@@ -4882,7 +4887,7 @@
         <v>20</v>
       </c>
       <c r="R26" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.4">
@@ -4911,7 +4916,7 @@
         <v>20</v>
       </c>
       <c r="R27" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.4">
@@ -4943,7 +4948,7 @@
         <v>20</v>
       </c>
       <c r="R28" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.4">
@@ -4975,7 +4980,7 @@
         <v>20</v>
       </c>
       <c r="R29" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.4">
@@ -5007,7 +5012,7 @@
         <v>20</v>
       </c>
       <c r="R30" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.4">
@@ -5039,7 +5044,7 @@
         <v>20</v>
       </c>
       <c r="R31" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.4">
@@ -5071,7 +5076,7 @@
         <v>20</v>
       </c>
       <c r="R32" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.4">
@@ -5103,7 +5108,7 @@
         <v>20</v>
       </c>
       <c r="R33" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.4">
@@ -5135,7 +5140,7 @@
         <v>20</v>
       </c>
       <c r="R34" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.4">
@@ -5164,7 +5169,7 @@
         <v>20</v>
       </c>
       <c r="R35" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.4">
@@ -5196,7 +5201,7 @@
         <v>33</v>
       </c>
       <c r="R36" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.4">
@@ -5228,7 +5233,7 @@
         <v>20</v>
       </c>
       <c r="R37" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.4">
@@ -5260,7 +5265,7 @@
         <v>20</v>
       </c>
       <c r="R38" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.4">
@@ -5292,7 +5297,7 @@
         <v>20</v>
       </c>
       <c r="R39" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.4">
@@ -5324,7 +5329,7 @@
         <v>20</v>
       </c>
       <c r="R40" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.4">
@@ -5356,7 +5361,7 @@
         <v>20</v>
       </c>
       <c r="R41" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.4">
@@ -5388,7 +5393,7 @@
         <v>20</v>
       </c>
       <c r="R42" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
     </row>
     <row r="43" spans="1:18" x14ac:dyDescent="0.4">
@@ -5417,7 +5422,7 @@
         <v>20</v>
       </c>
       <c r="R43" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
     </row>
     <row r="44" spans="1:18" x14ac:dyDescent="0.4">
@@ -5446,7 +5451,7 @@
         <v>20</v>
       </c>
       <c r="R44" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.4">
@@ -5475,7 +5480,7 @@
         <v>20</v>
       </c>
       <c r="R45" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
     </row>
     <row r="46" spans="1:18" x14ac:dyDescent="0.4">
@@ -5504,7 +5509,7 @@
         <v>20</v>
       </c>
       <c r="R46" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
     </row>
     <row r="47" spans="1:18" x14ac:dyDescent="0.4">
@@ -5533,7 +5538,7 @@
         <v>20</v>
       </c>
       <c r="R47" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
     </row>
     <row r="48" spans="1:18" x14ac:dyDescent="0.4">
@@ -5562,7 +5567,7 @@
         <v>20</v>
       </c>
       <c r="R48" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="49" spans="1:18" x14ac:dyDescent="0.4">
@@ -5591,7 +5596,7 @@
         <v>20</v>
       </c>
       <c r="R49" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="50" spans="1:18" x14ac:dyDescent="0.4">
@@ -5620,7 +5625,7 @@
         <v>20</v>
       </c>
       <c r="R50" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="51" spans="1:18" x14ac:dyDescent="0.4">
@@ -5652,7 +5657,7 @@
         <v>20</v>
       </c>
       <c r="R51" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
     </row>
     <row r="52" spans="1:18" x14ac:dyDescent="0.4">
@@ -5684,7 +5689,7 @@
         <v>20</v>
       </c>
       <c r="R52" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
     </row>
     <row r="53" spans="1:18" x14ac:dyDescent="0.4">
@@ -5716,7 +5721,7 @@
         <v>33</v>
       </c>
       <c r="R53" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
     </row>
     <row r="54" spans="1:18" x14ac:dyDescent="0.4">
@@ -5748,7 +5753,7 @@
         <v>20</v>
       </c>
       <c r="R54" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
     </row>
     <row r="55" spans="1:18" x14ac:dyDescent="0.4">
@@ -5777,7 +5782,7 @@
         <v>20</v>
       </c>
       <c r="R55" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
     </row>
     <row r="56" spans="1:18" x14ac:dyDescent="0.4">
@@ -5809,7 +5814,7 @@
         <v>20</v>
       </c>
       <c r="R56" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
     </row>
     <row r="57" spans="1:18" x14ac:dyDescent="0.4">
@@ -5841,7 +5846,7 @@
         <v>20</v>
       </c>
       <c r="R57" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
     </row>
     <row r="58" spans="1:18" x14ac:dyDescent="0.4">
@@ -5873,7 +5878,7 @@
         <v>33</v>
       </c>
       <c r="R58" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
     </row>
     <row r="59" spans="1:18" x14ac:dyDescent="0.4">
@@ -5902,7 +5907,7 @@
         <v>20</v>
       </c>
       <c r="R59" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
     </row>
     <row r="60" spans="1:18" x14ac:dyDescent="0.4">
@@ -5934,7 +5939,7 @@
         <v>20</v>
       </c>
       <c r="R60" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
     </row>
     <row r="61" spans="1:18" x14ac:dyDescent="0.4">
@@ -5963,7 +5968,7 @@
         <v>20</v>
       </c>
       <c r="R61" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
     </row>
     <row r="62" spans="1:18" x14ac:dyDescent="0.4">
@@ -5992,7 +5997,7 @@
         <v>33</v>
       </c>
       <c r="R62" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
     </row>
     <row r="63" spans="1:18" x14ac:dyDescent="0.4">
@@ -6030,7 +6035,7 @@
         <v>63</v>
       </c>
       <c r="R63" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
     </row>
     <row r="64" spans="1:18" x14ac:dyDescent="0.4">
@@ -6059,7 +6064,7 @@
         <v>20</v>
       </c>
       <c r="R64" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
     </row>
     <row r="65" spans="1:18" x14ac:dyDescent="0.4">
@@ -6088,7 +6093,7 @@
         <v>20</v>
       </c>
       <c r="R65" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
     </row>
     <row r="66" spans="1:18" x14ac:dyDescent="0.4">
@@ -6123,7 +6128,7 @@
         <v>64</v>
       </c>
       <c r="R66" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
     </row>
     <row r="67" spans="1:18" x14ac:dyDescent="0.4">
@@ -6155,7 +6160,7 @@
         <v>20</v>
       </c>
       <c r="R67" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="68" spans="1:18" x14ac:dyDescent="0.4">
@@ -6184,7 +6189,7 @@
         <v>20</v>
       </c>
       <c r="R68" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
     </row>
     <row r="69" spans="1:18" x14ac:dyDescent="0.4">
@@ -6213,7 +6218,7 @@
         <v>33</v>
       </c>
       <c r="R69" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
     </row>
     <row r="70" spans="1:18" x14ac:dyDescent="0.4">
@@ -6245,7 +6250,7 @@
         <v>20</v>
       </c>
       <c r="R70" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="71" spans="1:18" x14ac:dyDescent="0.4">
@@ -6277,7 +6282,7 @@
         <v>20</v>
       </c>
       <c r="R71" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
     </row>
     <row r="72" spans="1:18" x14ac:dyDescent="0.4">
@@ -6306,7 +6311,7 @@
         <v>20</v>
       </c>
       <c r="R72" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
     </row>
     <row r="73" spans="1:18" x14ac:dyDescent="0.4">
@@ -6335,7 +6340,7 @@
         <v>33</v>
       </c>
       <c r="R73" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="74" spans="1:18" x14ac:dyDescent="0.4">
@@ -6370,7 +6375,7 @@
         <v>64</v>
       </c>
       <c r="R74" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="75" spans="1:18" x14ac:dyDescent="0.4">
@@ -6402,7 +6407,7 @@
         <v>20</v>
       </c>
       <c r="R75" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
     </row>
     <row r="76" spans="1:18" x14ac:dyDescent="0.4">
@@ -6434,7 +6439,7 @@
         <v>33</v>
       </c>
       <c r="R76" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
     </row>
     <row r="77" spans="1:18" x14ac:dyDescent="0.4">
@@ -6466,7 +6471,7 @@
         <v>20</v>
       </c>
       <c r="R77" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
     </row>
     <row r="78" spans="1:18" x14ac:dyDescent="0.4">
@@ -6498,7 +6503,7 @@
         <v>20</v>
       </c>
       <c r="R78" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="79" spans="1:18" x14ac:dyDescent="0.4">
@@ -6530,7 +6535,7 @@
         <v>20</v>
       </c>
       <c r="R79" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="80" spans="1:18" x14ac:dyDescent="0.4">
@@ -6568,7 +6573,7 @@
         <v>80</v>
       </c>
       <c r="R80" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="81" spans="1:18" x14ac:dyDescent="0.4">
@@ -6597,7 +6602,7 @@
         <v>147</v>
       </c>
       <c r="R81" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
     </row>
     <row r="82" spans="1:18" x14ac:dyDescent="0.4">
@@ -6626,7 +6631,7 @@
         <v>20</v>
       </c>
       <c r="R82" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="83" spans="1:18" x14ac:dyDescent="0.4">
@@ -6664,7 +6669,7 @@
         <v>27</v>
       </c>
       <c r="R83" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="84" spans="1:18" x14ac:dyDescent="0.4">
@@ -6693,7 +6698,7 @@
         <v>33</v>
       </c>
       <c r="R84" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
     <row r="85" spans="1:18" x14ac:dyDescent="0.4">
@@ -6722,7 +6727,7 @@
         <v>20</v>
       </c>
       <c r="R85" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
     </row>
     <row r="86" spans="1:18" x14ac:dyDescent="0.4">
@@ -6751,7 +6756,7 @@
         <v>33</v>
       </c>
       <c r="R86" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
     </row>
     <row r="87" spans="1:18" x14ac:dyDescent="0.4">
@@ -6780,7 +6785,7 @@
         <v>20</v>
       </c>
       <c r="R87" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
     </row>
     <row r="88" spans="1:18" x14ac:dyDescent="0.4">
@@ -6812,7 +6817,7 @@
         <v>20</v>
       </c>
       <c r="R88" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="89" spans="1:18" x14ac:dyDescent="0.4">
@@ -6850,7 +6855,7 @@
         <v>27</v>
       </c>
       <c r="R89" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
     </row>
     <row r="90" spans="1:18" x14ac:dyDescent="0.4">
@@ -6882,7 +6887,7 @@
         <v>20</v>
       </c>
       <c r="R90" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
     </row>
     <row r="91" spans="1:18" x14ac:dyDescent="0.4">
@@ -6914,7 +6919,7 @@
         <v>20</v>
       </c>
       <c r="R91" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
     </row>
     <row r="92" spans="1:18" x14ac:dyDescent="0.4">
@@ -6946,7 +6951,7 @@
         <v>20</v>
       </c>
       <c r="R92" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
     </row>
     <row r="93" spans="1:18" x14ac:dyDescent="0.4">
@@ -6978,7 +6983,7 @@
         <v>20</v>
       </c>
       <c r="R93" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="94" spans="1:18" x14ac:dyDescent="0.4">
@@ -7010,7 +7015,7 @@
         <v>20</v>
       </c>
       <c r="R94" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
     </row>
     <row r="95" spans="1:18" x14ac:dyDescent="0.4">
@@ -7042,7 +7047,7 @@
         <v>20</v>
       </c>
       <c r="R95" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
     </row>
     <row r="96" spans="1:18" x14ac:dyDescent="0.4">
@@ -7074,7 +7079,7 @@
         <v>20</v>
       </c>
       <c r="R96" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
     </row>
     <row r="97" spans="1:18" x14ac:dyDescent="0.4">
@@ -7106,7 +7111,7 @@
         <v>20</v>
       </c>
       <c r="R97" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
     </row>
     <row r="98" spans="1:18" x14ac:dyDescent="0.4">
@@ -7135,7 +7140,7 @@
         <v>33</v>
       </c>
       <c r="R98" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
     </row>
     <row r="99" spans="1:18" x14ac:dyDescent="0.4">
@@ -7164,7 +7169,7 @@
         <v>20</v>
       </c>
       <c r="R99" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="100" spans="1:18" x14ac:dyDescent="0.4">
@@ -7196,7 +7201,7 @@
         <v>20</v>
       </c>
       <c r="R100" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
     </row>
     <row r="101" spans="1:18" x14ac:dyDescent="0.4">
@@ -7228,7 +7233,7 @@
         <v>20</v>
       </c>
       <c r="R101" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
     </row>
     <row r="102" spans="1:18" x14ac:dyDescent="0.4">
@@ -7257,7 +7262,7 @@
         <v>20</v>
       </c>
       <c r="R102" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
     </row>
     <row r="103" spans="1:18" x14ac:dyDescent="0.4">
@@ -7286,7 +7291,7 @@
         <v>20</v>
       </c>
       <c r="R103" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
     </row>
     <row r="104" spans="1:18" x14ac:dyDescent="0.4">
@@ -7318,7 +7323,7 @@
         <v>175</v>
       </c>
       <c r="R104" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
     </row>
     <row r="105" spans="1:18" x14ac:dyDescent="0.4">
@@ -7347,7 +7352,7 @@
         <v>20</v>
       </c>
       <c r="R105" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
     </row>
     <row r="106" spans="1:18" x14ac:dyDescent="0.4">
@@ -7382,7 +7387,7 @@
         <v>41</v>
       </c>
       <c r="R106" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
     </row>
     <row r="107" spans="1:18" x14ac:dyDescent="0.4">
@@ -7417,7 +7422,7 @@
         <v>21</v>
       </c>
       <c r="R107" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="108" spans="1:18" x14ac:dyDescent="0.4">
@@ -7446,7 +7451,7 @@
         <v>20</v>
       </c>
       <c r="R108" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="109" spans="1:18" x14ac:dyDescent="0.4">
@@ -7478,7 +7483,7 @@
         <v>20</v>
       </c>
       <c r="R109" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="110" spans="1:18" x14ac:dyDescent="0.4">
@@ -7507,7 +7512,7 @@
         <v>20</v>
       </c>
       <c r="R110" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="111" spans="1:18" x14ac:dyDescent="0.4">
@@ -7536,7 +7541,7 @@
         <v>20</v>
       </c>
       <c r="R111" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="112" spans="1:18" x14ac:dyDescent="0.4">
@@ -7574,7 +7579,7 @@
         <v>27</v>
       </c>
       <c r="R112" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
     </row>
     <row r="113" spans="1:18" x14ac:dyDescent="0.4">
@@ -7603,7 +7608,7 @@
         <v>20</v>
       </c>
       <c r="R113" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="114" spans="1:18" x14ac:dyDescent="0.4">
@@ -7632,7 +7637,7 @@
         <v>20</v>
       </c>
       <c r="R114" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
     </row>
     <row r="115" spans="1:18" x14ac:dyDescent="0.4">
@@ -7661,7 +7666,7 @@
         <v>33</v>
       </c>
       <c r="R115" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
     </row>
     <row r="116" spans="1:18" x14ac:dyDescent="0.4">
@@ -7696,7 +7701,7 @@
         <v>21</v>
       </c>
       <c r="R116" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
     </row>
     <row r="117" spans="1:18" x14ac:dyDescent="0.4">
@@ -7731,7 +7736,7 @@
         <v>80</v>
       </c>
       <c r="R117" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
     </row>
     <row r="118" spans="1:18" x14ac:dyDescent="0.4">
@@ -7766,7 +7771,7 @@
         <v>41</v>
       </c>
       <c r="R118" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
     </row>
     <row r="119" spans="1:18" x14ac:dyDescent="0.4">
@@ -7798,7 +7803,7 @@
         <v>20</v>
       </c>
       <c r="R119" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="120" spans="1:18" x14ac:dyDescent="0.4">
@@ -7833,7 +7838,7 @@
         <v>27</v>
       </c>
       <c r="R120" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
     </row>
     <row r="121" spans="1:18" x14ac:dyDescent="0.4">
@@ -7865,7 +7870,7 @@
         <v>20</v>
       </c>
       <c r="R121" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
     </row>
     <row r="122" spans="1:18" x14ac:dyDescent="0.4">
@@ -7897,7 +7902,7 @@
         <v>20</v>
       </c>
       <c r="R122" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
     </row>
     <row r="123" spans="1:18" x14ac:dyDescent="0.4">
@@ -7929,7 +7934,7 @@
         <v>20</v>
       </c>
       <c r="R123" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
     </row>
     <row r="124" spans="1:18" x14ac:dyDescent="0.4">
@@ -7961,7 +7966,7 @@
         <v>20</v>
       </c>
       <c r="R124" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
     </row>
     <row r="125" spans="1:18" x14ac:dyDescent="0.4">
@@ -7993,7 +7998,7 @@
         <v>33</v>
       </c>
       <c r="R125" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
     </row>
     <row r="126" spans="1:18" x14ac:dyDescent="0.4">
@@ -8025,7 +8030,7 @@
         <v>20</v>
       </c>
       <c r="R126" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
     </row>
     <row r="127" spans="1:18" x14ac:dyDescent="0.4">
@@ -8057,7 +8062,7 @@
         <v>20</v>
       </c>
       <c r="R127" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="128" spans="1:18" x14ac:dyDescent="0.4">
@@ -8089,7 +8094,7 @@
         <v>20</v>
       </c>
       <c r="R128" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="129" spans="1:18" x14ac:dyDescent="0.4">
@@ -8121,7 +8126,7 @@
         <v>20</v>
       </c>
       <c r="R129" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="130" spans="1:18" x14ac:dyDescent="0.4">
@@ -8159,7 +8164,7 @@
         <v>41</v>
       </c>
       <c r="R130" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
     </row>
     <row r="131" spans="1:18" x14ac:dyDescent="0.4">
@@ -8194,7 +8199,7 @@
         <v>41</v>
       </c>
       <c r="R131" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
     </row>
     <row r="132" spans="1:18" x14ac:dyDescent="0.4">
@@ -8226,7 +8231,7 @@
         <v>20</v>
       </c>
       <c r="R132" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
     </row>
     <row r="133" spans="1:18" x14ac:dyDescent="0.4">
@@ -8258,7 +8263,7 @@
         <v>20</v>
       </c>
       <c r="R133" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
     </row>
     <row r="134" spans="1:18" x14ac:dyDescent="0.4">
@@ -8290,7 +8295,7 @@
         <v>20</v>
       </c>
       <c r="R134" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
     </row>
     <row r="135" spans="1:18" x14ac:dyDescent="0.4">
@@ -8319,7 +8324,7 @@
         <v>20</v>
       </c>
       <c r="R135" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
     </row>
     <row r="136" spans="1:18" x14ac:dyDescent="0.4">
@@ -8348,7 +8353,7 @@
         <v>20</v>
       </c>
       <c r="R136" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
     </row>
     <row r="137" spans="1:18" x14ac:dyDescent="0.4">
@@ -8380,7 +8385,7 @@
         <v>20</v>
       </c>
       <c r="R137" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
     </row>
     <row r="138" spans="1:18" x14ac:dyDescent="0.4">
@@ -8415,7 +8420,7 @@
         <v>28</v>
       </c>
       <c r="R138" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
     </row>
     <row r="139" spans="1:18" x14ac:dyDescent="0.4">
@@ -8450,7 +8455,7 @@
         <v>175</v>
       </c>
       <c r="R139" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
     </row>
     <row r="140" spans="1:18" x14ac:dyDescent="0.4">
@@ -8482,7 +8487,7 @@
         <v>20</v>
       </c>
       <c r="R140" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
     </row>
     <row r="141" spans="1:18" x14ac:dyDescent="0.4">
@@ -8511,7 +8516,7 @@
         <v>20</v>
       </c>
       <c r="R141" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
     </row>
     <row r="142" spans="1:18" x14ac:dyDescent="0.4">
@@ -8543,7 +8548,7 @@
         <v>20</v>
       </c>
       <c r="R142" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
     </row>
     <row r="143" spans="1:18" x14ac:dyDescent="0.4">
@@ -8578,7 +8583,7 @@
         <v>229</v>
       </c>
       <c r="R143" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
     </row>
     <row r="144" spans="1:18" x14ac:dyDescent="0.4">
@@ -8610,7 +8615,7 @@
         <v>20</v>
       </c>
       <c r="R144" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
     </row>
     <row r="145" spans="1:18" x14ac:dyDescent="0.4">
@@ -8639,7 +8644,7 @@
         <v>20</v>
       </c>
       <c r="R145" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
     </row>
     <row r="146" spans="1:18" x14ac:dyDescent="0.4">
@@ -8668,7 +8673,7 @@
         <v>20</v>
       </c>
       <c r="R146" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
     </row>
     <row r="147" spans="1:18" x14ac:dyDescent="0.4">
@@ -8700,7 +8705,7 @@
         <v>20</v>
       </c>
       <c r="R147" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
     </row>
     <row r="148" spans="1:18" x14ac:dyDescent="0.4">
@@ -8735,7 +8740,7 @@
         <v>229</v>
       </c>
       <c r="R148" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
     </row>
     <row r="149" spans="1:18" x14ac:dyDescent="0.4">
@@ -8770,7 +8775,7 @@
         <v>42</v>
       </c>
       <c r="R149" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
     </row>
     <row r="150" spans="1:18" x14ac:dyDescent="0.4">
@@ -8802,7 +8807,7 @@
         <v>20</v>
       </c>
       <c r="R150" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
     </row>
     <row r="151" spans="1:18" x14ac:dyDescent="0.4">
@@ -8831,7 +8836,7 @@
         <v>20</v>
       </c>
       <c r="R151" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
     </row>
     <row r="152" spans="1:18" x14ac:dyDescent="0.4">
@@ -8866,7 +8871,7 @@
         <v>41</v>
       </c>
       <c r="R152" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
     </row>
     <row r="153" spans="1:18" x14ac:dyDescent="0.4">
@@ -8898,7 +8903,7 @@
         <v>21</v>
       </c>
       <c r="R153" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
     </row>
     <row r="154" spans="1:18" x14ac:dyDescent="0.4">
@@ -8930,7 +8935,7 @@
         <v>20</v>
       </c>
       <c r="R154" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
     </row>
     <row r="155" spans="1:18" x14ac:dyDescent="0.4">
@@ -8959,7 +8964,7 @@
         <v>20</v>
       </c>
       <c r="R155" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
     </row>
     <row r="156" spans="1:18" x14ac:dyDescent="0.4">
@@ -8988,7 +8993,7 @@
         <v>20</v>
       </c>
       <c r="R156" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="157" spans="1:18" x14ac:dyDescent="0.4">
@@ -9017,7 +9022,7 @@
         <v>20</v>
       </c>
       <c r="R157" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
     </row>
     <row r="158" spans="1:18" x14ac:dyDescent="0.4">
@@ -9046,7 +9051,7 @@
         <v>20</v>
       </c>
       <c r="R158" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="159" spans="1:18" x14ac:dyDescent="0.4">
@@ -9075,7 +9080,7 @@
         <v>20</v>
       </c>
       <c r="R159" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
     </row>
     <row r="160" spans="1:18" x14ac:dyDescent="0.4">
@@ -9107,7 +9112,7 @@
         <v>27</v>
       </c>
       <c r="R160" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
     </row>
     <row r="161" spans="1:18" x14ac:dyDescent="0.4">
@@ -9139,7 +9144,7 @@
         <v>20</v>
       </c>
       <c r="R161" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
     <row r="162" spans="1:18" x14ac:dyDescent="0.4">
@@ -9171,7 +9176,7 @@
         <v>20</v>
       </c>
       <c r="R162" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
     </row>
     <row r="163" spans="1:18" x14ac:dyDescent="0.4">
@@ -9200,7 +9205,7 @@
         <v>20</v>
       </c>
       <c r="R163" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
     </row>
     <row r="164" spans="1:18" x14ac:dyDescent="0.4">
@@ -9229,7 +9234,7 @@
         <v>20</v>
       </c>
       <c r="R164" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
     </row>
     <row r="165" spans="1:18" x14ac:dyDescent="0.4">
@@ -9258,7 +9263,7 @@
         <v>20</v>
       </c>
       <c r="R165" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
     </row>
     <row r="166" spans="1:18" x14ac:dyDescent="0.4">
@@ -9290,7 +9295,7 @@
         <v>20</v>
       </c>
       <c r="R166" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
     </row>
     <row r="167" spans="1:18" x14ac:dyDescent="0.4">
@@ -9319,7 +9324,7 @@
         <v>20</v>
       </c>
       <c r="R167" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
     </row>
     <row r="168" spans="1:18" x14ac:dyDescent="0.4">
@@ -9351,7 +9356,7 @@
         <v>63</v>
       </c>
       <c r="R168" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
     </row>
     <row r="169" spans="1:18" x14ac:dyDescent="0.4">
@@ -9386,7 +9391,7 @@
         <v>80</v>
       </c>
       <c r="R169" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
     </row>
     <row r="170" spans="1:18" x14ac:dyDescent="0.4">
@@ -9415,7 +9420,7 @@
         <v>20</v>
       </c>
       <c r="R170" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
     </row>
     <row r="171" spans="1:18" x14ac:dyDescent="0.4">
@@ -9453,7 +9458,7 @@
         <v>175</v>
       </c>
       <c r="R171" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
     </row>
     <row r="172" spans="1:18" x14ac:dyDescent="0.4">
@@ -9485,7 +9490,7 @@
         <v>21</v>
       </c>
       <c r="R172" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="173" spans="1:18" x14ac:dyDescent="0.4">
@@ -9514,7 +9519,7 @@
         <v>20</v>
       </c>
       <c r="R173" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="174" spans="1:18" x14ac:dyDescent="0.4">
@@ -9543,7 +9548,7 @@
         <v>33</v>
       </c>
       <c r="R174" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="175" spans="1:18" x14ac:dyDescent="0.4">
@@ -9572,7 +9577,7 @@
         <v>20</v>
       </c>
       <c r="R175" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="176" spans="1:18" x14ac:dyDescent="0.4">
@@ -9601,7 +9606,7 @@
         <v>20</v>
       </c>
       <c r="R176" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
     </row>
     <row r="177" spans="1:18" x14ac:dyDescent="0.4">
@@ -9630,7 +9635,7 @@
         <v>33</v>
       </c>
       <c r="R177" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
     </row>
     <row r="178" spans="1:18" x14ac:dyDescent="0.4">
@@ -9662,7 +9667,7 @@
         <v>20</v>
       </c>
       <c r="R178" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="179" spans="1:18" x14ac:dyDescent="0.4">
@@ -9670,7 +9675,7 @@
         <v>477</v>
       </c>
       <c r="B179" t="s">
-        <v>269</v>
+        <v>977</v>
       </c>
       <c r="C179">
         <v>451</v>
@@ -9688,7 +9693,7 @@
         <v>85</v>
       </c>
       <c r="H179" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="I179" t="s">
         <v>33</v>
@@ -9715,7 +9720,7 @@
         <v>41</v>
       </c>
       <c r="R179" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
     </row>
     <row r="180" spans="1:18" x14ac:dyDescent="0.4">
@@ -9723,7 +9728,7 @@
         <v>480</v>
       </c>
       <c r="B180" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C180">
         <v>452</v>
@@ -9744,7 +9749,7 @@
         <v>20</v>
       </c>
       <c r="R180" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
     </row>
     <row r="181" spans="1:18" x14ac:dyDescent="0.4">
@@ -9752,7 +9757,7 @@
         <v>483</v>
       </c>
       <c r="B181" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C181">
         <v>455</v>
@@ -9773,7 +9778,7 @@
         <v>20</v>
       </c>
       <c r="R181" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="182" spans="1:18" x14ac:dyDescent="0.4">
@@ -9781,7 +9786,7 @@
         <v>484</v>
       </c>
       <c r="B182" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C182">
         <v>456</v>
@@ -9802,7 +9807,7 @@
         <v>20</v>
       </c>
       <c r="R182" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="183" spans="1:18" x14ac:dyDescent="0.4">
@@ -9810,7 +9815,7 @@
         <v>494</v>
       </c>
       <c r="B183" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C183">
         <v>490</v>
@@ -9825,7 +9830,7 @@
         <v>45</v>
       </c>
       <c r="G183" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H183" t="s">
         <v>56</v>
@@ -9834,7 +9839,7 @@
         <v>33</v>
       </c>
       <c r="R183" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="184" spans="1:18" x14ac:dyDescent="0.4">
@@ -9842,7 +9847,7 @@
         <v>495</v>
       </c>
       <c r="B184" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C184">
         <v>491</v>
@@ -9857,16 +9862,16 @@
         <v>51</v>
       </c>
       <c r="G184" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H184" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="I184" t="s">
         <v>20</v>
       </c>
       <c r="R184" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
     </row>
     <row r="185" spans="1:18" x14ac:dyDescent="0.4">
@@ -9874,7 +9879,7 @@
         <v>496</v>
       </c>
       <c r="B185" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C185">
         <v>492</v>
@@ -9895,7 +9900,7 @@
         <v>20</v>
       </c>
       <c r="R185" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="186" spans="1:18" x14ac:dyDescent="0.4">
@@ -9903,7 +9908,7 @@
         <v>504</v>
       </c>
       <c r="B186" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C186">
         <v>497</v>
@@ -9930,7 +9935,7 @@
         <v>40</v>
       </c>
       <c r="R186" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
     </row>
     <row r="187" spans="1:18" x14ac:dyDescent="0.4">
@@ -9938,7 +9943,7 @@
         <v>505</v>
       </c>
       <c r="B187" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C187">
         <v>497</v>
@@ -9965,7 +9970,7 @@
         <v>80</v>
       </c>
       <c r="R187" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
     </row>
     <row r="188" spans="1:18" x14ac:dyDescent="0.4">
@@ -9973,7 +9978,7 @@
         <v>509</v>
       </c>
       <c r="B188" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C188">
         <v>498</v>
@@ -9994,7 +9999,7 @@
         <v>33</v>
       </c>
       <c r="R188" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
     </row>
     <row r="189" spans="1:18" x14ac:dyDescent="0.4">
@@ -10002,7 +10007,7 @@
         <v>510</v>
       </c>
       <c r="B189" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C189">
         <v>498</v>
@@ -10029,7 +10034,7 @@
         <v>63</v>
       </c>
       <c r="R189" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
     </row>
     <row r="190" spans="1:18" x14ac:dyDescent="0.4">
@@ -10037,7 +10042,7 @@
         <v>511</v>
       </c>
       <c r="B190" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C190">
         <v>498</v>
@@ -10061,7 +10066,7 @@
         <v>27</v>
       </c>
       <c r="R190" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
     </row>
     <row r="191" spans="1:18" x14ac:dyDescent="0.4">
@@ -10069,7 +10074,7 @@
         <v>512</v>
       </c>
       <c r="B191" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C191">
         <v>498</v>
@@ -10090,7 +10095,7 @@
         <v>20</v>
       </c>
       <c r="R191" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
     </row>
     <row r="192" spans="1:18" x14ac:dyDescent="0.4">
@@ -10098,7 +10103,7 @@
         <v>513</v>
       </c>
       <c r="B192" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C192">
         <v>498</v>
@@ -10116,13 +10121,13 @@
         <v>52</v>
       </c>
       <c r="H192" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="I192" t="s">
         <v>20</v>
       </c>
       <c r="R192" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
     </row>
     <row r="193" spans="1:18" x14ac:dyDescent="0.4">
@@ -10130,7 +10135,7 @@
         <v>514</v>
       </c>
       <c r="B193" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C193">
         <v>498</v>
@@ -10151,7 +10156,7 @@
         <v>20</v>
       </c>
       <c r="R193" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
     </row>
     <row r="194" spans="1:18" x14ac:dyDescent="0.4">
@@ -10159,7 +10164,7 @@
         <v>515</v>
       </c>
       <c r="B194" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C194">
         <v>498</v>
@@ -10183,7 +10188,7 @@
         <v>21</v>
       </c>
       <c r="R194" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="195" spans="1:18" x14ac:dyDescent="0.4">
@@ -10191,7 +10196,7 @@
         <v>516</v>
       </c>
       <c r="B195" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C195">
         <v>498</v>
@@ -10212,7 +10217,7 @@
         <v>20</v>
       </c>
       <c r="R195" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
     </row>
     <row r="196" spans="1:18" x14ac:dyDescent="0.4">
@@ -10220,7 +10225,7 @@
         <v>517</v>
       </c>
       <c r="B196" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C196">
         <v>498</v>
@@ -10241,7 +10246,7 @@
         <v>20</v>
       </c>
       <c r="R196" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="197" spans="1:18" x14ac:dyDescent="0.4">
@@ -10249,7 +10254,7 @@
         <v>518</v>
       </c>
       <c r="B197" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C197">
         <v>498</v>
@@ -10267,7 +10272,7 @@
         <v>103</v>
       </c>
       <c r="H197" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="I197" t="s">
         <v>20</v>
@@ -10276,7 +10281,7 @@
         <v>229</v>
       </c>
       <c r="R197" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="198" spans="1:18" x14ac:dyDescent="0.4">
@@ -10284,7 +10289,7 @@
         <v>520</v>
       </c>
       <c r="B198" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C198">
         <v>500</v>
@@ -10299,7 +10304,7 @@
         <v>36</v>
       </c>
       <c r="G198" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="I198" t="s">
         <v>20</v>
@@ -10308,7 +10313,7 @@
         <v>40</v>
       </c>
       <c r="R198" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
     </row>
     <row r="199" spans="1:18" x14ac:dyDescent="0.4">
@@ -10316,7 +10321,7 @@
         <v>523</v>
       </c>
       <c r="B199" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C199">
         <v>499</v>
@@ -10343,7 +10348,7 @@
         <v>229</v>
       </c>
       <c r="R199" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="200" spans="1:18" x14ac:dyDescent="0.4">
@@ -10351,7 +10356,7 @@
         <v>531</v>
       </c>
       <c r="B200" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C200">
         <v>500</v>
@@ -10372,7 +10377,7 @@
         <v>20</v>
       </c>
       <c r="R200" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
     </row>
     <row r="201" spans="1:18" x14ac:dyDescent="0.4">
@@ -10380,7 +10385,7 @@
         <v>538</v>
       </c>
       <c r="B201" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C201">
         <v>507</v>
@@ -10401,7 +10406,7 @@
         <v>20</v>
       </c>
       <c r="R201" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
     </row>
     <row r="202" spans="1:18" x14ac:dyDescent="0.4">
@@ -10409,7 +10414,7 @@
         <v>541</v>
       </c>
       <c r="B202" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C202">
         <v>511</v>
@@ -10427,13 +10432,13 @@
         <v>44</v>
       </c>
       <c r="H202" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="I202" t="s">
         <v>20</v>
       </c>
       <c r="R202" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
     </row>
     <row r="203" spans="1:18" x14ac:dyDescent="0.4">
@@ -10441,7 +10446,7 @@
         <v>543</v>
       </c>
       <c r="B203" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C203">
         <v>514</v>
@@ -10456,16 +10461,16 @@
         <v>55</v>
       </c>
       <c r="G203" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H203" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="I203" t="s">
         <v>33</v>
       </c>
       <c r="R203" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
     </row>
     <row r="204" spans="1:18" x14ac:dyDescent="0.4">
@@ -10473,7 +10478,7 @@
         <v>557</v>
       </c>
       <c r="B204" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C204">
         <v>516</v>
@@ -10488,10 +10493,10 @@
         <v>36</v>
       </c>
       <c r="G204" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H204" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="I204" t="s">
         <v>33</v>
@@ -10500,7 +10505,7 @@
         <v>229</v>
       </c>
       <c r="R204" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="205" spans="1:18" x14ac:dyDescent="0.4">
@@ -10508,7 +10513,7 @@
         <v>558</v>
       </c>
       <c r="B205" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C205">
         <v>516</v>
@@ -10523,10 +10528,10 @@
         <v>36</v>
       </c>
       <c r="G205" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H205" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="I205" t="s">
         <v>33</v>
@@ -10538,7 +10543,7 @@
         <v>229</v>
       </c>
       <c r="R205" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="206" spans="1:18" x14ac:dyDescent="0.4">
@@ -10546,7 +10551,7 @@
         <v>559</v>
       </c>
       <c r="B206" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C206">
         <v>516</v>
@@ -10561,10 +10566,10 @@
         <v>36</v>
       </c>
       <c r="G206" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H206" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="I206" t="s">
         <v>33</v>
@@ -10573,7 +10578,7 @@
         <v>42</v>
       </c>
       <c r="R206" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
     </row>
     <row r="207" spans="1:18" x14ac:dyDescent="0.4">
@@ -10581,7 +10586,7 @@
         <v>564</v>
       </c>
       <c r="B207" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C207">
         <v>523</v>
@@ -10596,7 +10601,7 @@
         <v>45</v>
       </c>
       <c r="G207" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H207" t="s">
         <v>197</v>
@@ -10605,7 +10610,7 @@
         <v>20</v>
       </c>
       <c r="R207" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
     </row>
     <row r="208" spans="1:18" x14ac:dyDescent="0.4">
@@ -10613,7 +10618,7 @@
         <v>567</v>
       </c>
       <c r="B208" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C208">
         <v>524</v>
@@ -10634,7 +10639,7 @@
         <v>20</v>
       </c>
       <c r="R208" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="209" spans="1:18" x14ac:dyDescent="0.4">
@@ -10642,7 +10647,7 @@
         <v>571</v>
       </c>
       <c r="B209" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C209">
         <v>526</v>
@@ -10663,7 +10668,7 @@
         <v>20</v>
       </c>
       <c r="R209" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
     </row>
     <row r="210" spans="1:18" x14ac:dyDescent="0.4">
@@ -10671,7 +10676,7 @@
         <v>575</v>
       </c>
       <c r="B210" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C210">
         <v>528</v>
@@ -10692,7 +10697,7 @@
         <v>20</v>
       </c>
       <c r="R210" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
     </row>
     <row r="211" spans="1:18" x14ac:dyDescent="0.4">
@@ -10700,7 +10705,7 @@
         <v>580</v>
       </c>
       <c r="B211" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C211">
         <v>530</v>
@@ -10721,7 +10726,7 @@
         <v>20</v>
       </c>
       <c r="R211" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
     </row>
     <row r="212" spans="1:18" x14ac:dyDescent="0.4">
@@ -10729,7 +10734,7 @@
         <v>582</v>
       </c>
       <c r="B212" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C212">
         <v>531</v>
@@ -10750,7 +10755,7 @@
         <v>33</v>
       </c>
       <c r="R212" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
     </row>
     <row r="213" spans="1:18" x14ac:dyDescent="0.4">
@@ -10758,7 +10763,7 @@
         <v>588</v>
       </c>
       <c r="B213" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C213">
         <v>537</v>
@@ -10779,7 +10784,7 @@
         <v>147</v>
       </c>
       <c r="R213" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
     </row>
     <row r="214" spans="1:18" x14ac:dyDescent="0.4">
@@ -10787,7 +10792,7 @@
         <v>589</v>
       </c>
       <c r="B214" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C214">
         <v>537</v>
@@ -10805,13 +10810,13 @@
         <v>85</v>
       </c>
       <c r="H214" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="I214" t="s">
         <v>147</v>
       </c>
       <c r="R214" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
     </row>
     <row r="215" spans="1:18" x14ac:dyDescent="0.4">
@@ -10819,7 +10824,7 @@
         <v>591</v>
       </c>
       <c r="B215" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C215">
         <v>542</v>
@@ -10840,7 +10845,7 @@
         <v>20</v>
       </c>
       <c r="R215" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="216" spans="1:18" x14ac:dyDescent="0.4">
@@ -10848,7 +10853,7 @@
         <v>595</v>
       </c>
       <c r="B216" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C216">
         <v>397</v>
@@ -10869,7 +10874,7 @@
         <v>20</v>
       </c>
       <c r="R216" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
     </row>
     <row r="217" spans="1:18" x14ac:dyDescent="0.4">
@@ -10877,7 +10882,7 @@
         <v>600</v>
       </c>
       <c r="B217" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C217">
         <v>551</v>
@@ -10898,7 +10903,7 @@
         <v>20</v>
       </c>
       <c r="R217" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="218" spans="1:18" x14ac:dyDescent="0.4">
@@ -10906,7 +10911,7 @@
         <v>606</v>
       </c>
       <c r="B218" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C218">
         <v>552</v>
@@ -10927,7 +10932,7 @@
         <v>20</v>
       </c>
       <c r="R218" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
     </row>
     <row r="219" spans="1:18" x14ac:dyDescent="0.4">
@@ -10935,7 +10940,7 @@
         <v>614</v>
       </c>
       <c r="B219" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C219">
         <v>553</v>
@@ -10953,7 +10958,7 @@
         <v>268</v>
       </c>
       <c r="H219" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="I219" t="s">
         <v>20</v>
@@ -10962,7 +10967,7 @@
         <v>41</v>
       </c>
       <c r="R219" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
     </row>
     <row r="220" spans="1:18" x14ac:dyDescent="0.4">
@@ -10970,7 +10975,7 @@
         <v>627</v>
       </c>
       <c r="B220" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C220">
         <v>554</v>
@@ -10991,7 +10996,7 @@
         <v>20</v>
       </c>
       <c r="R220" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
     </row>
     <row r="221" spans="1:18" x14ac:dyDescent="0.4">
@@ -10999,7 +11004,7 @@
         <v>648</v>
       </c>
       <c r="B221" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C221">
         <v>576</v>
@@ -11020,7 +11025,7 @@
         <v>20</v>
       </c>
       <c r="R221" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="222" spans="1:18" x14ac:dyDescent="0.4">
@@ -11028,7 +11033,7 @@
         <v>649</v>
       </c>
       <c r="B222" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C222">
         <v>576</v>
@@ -11049,7 +11054,7 @@
         <v>20</v>
       </c>
       <c r="R222" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="223" spans="1:18" x14ac:dyDescent="0.4">
@@ -11057,7 +11062,7 @@
         <v>650</v>
       </c>
       <c r="B223" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C223">
         <v>576</v>
@@ -11078,7 +11083,7 @@
         <v>33</v>
       </c>
       <c r="R223" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="224" spans="1:18" x14ac:dyDescent="0.4">
@@ -11086,7 +11091,7 @@
         <v>651</v>
       </c>
       <c r="B224" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C224">
         <v>576</v>
@@ -11107,7 +11112,7 @@
         <v>20</v>
       </c>
       <c r="R224" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="225" spans="1:18" x14ac:dyDescent="0.4">
@@ -11115,7 +11120,7 @@
         <v>655</v>
       </c>
       <c r="B225" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C225">
         <v>581</v>
@@ -11136,7 +11141,7 @@
         <v>20</v>
       </c>
       <c r="R225" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
     </row>
     <row r="226" spans="1:18" x14ac:dyDescent="0.4">
@@ -11144,7 +11149,7 @@
         <v>656</v>
       </c>
       <c r="B226" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C226">
         <v>582</v>
@@ -11162,13 +11167,13 @@
         <v>17</v>
       </c>
       <c r="H226" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="I226" t="s">
         <v>33</v>
       </c>
       <c r="R226" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
     </row>
     <row r="227" spans="1:18" x14ac:dyDescent="0.4">
@@ -11176,7 +11181,7 @@
         <v>659</v>
       </c>
       <c r="B227" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C227">
         <v>583</v>
@@ -11206,7 +11211,7 @@
         <v>27</v>
       </c>
       <c r="R227" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="228" spans="1:18" x14ac:dyDescent="0.4">
@@ -11214,7 +11219,7 @@
         <v>660</v>
       </c>
       <c r="B228" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C228">
         <v>583</v>
@@ -11238,7 +11243,7 @@
         <v>20</v>
       </c>
       <c r="R228" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
     </row>
     <row r="229" spans="1:18" x14ac:dyDescent="0.4">
@@ -11246,7 +11251,7 @@
         <v>661</v>
       </c>
       <c r="B229" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C229">
         <v>584</v>
@@ -11270,7 +11275,7 @@
         <v>20</v>
       </c>
       <c r="R229" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
     </row>
     <row r="230" spans="1:18" x14ac:dyDescent="0.4">
@@ -11278,7 +11283,7 @@
         <v>664</v>
       </c>
       <c r="B230" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C230">
         <v>586</v>
@@ -11305,7 +11310,7 @@
         <v>64</v>
       </c>
       <c r="R230" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
     </row>
     <row r="231" spans="1:18" x14ac:dyDescent="0.4">
@@ -11313,7 +11318,7 @@
         <v>680</v>
       </c>
       <c r="B231" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C231">
         <v>598</v>
@@ -11334,7 +11339,7 @@
         <v>20</v>
       </c>
       <c r="R231" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
     </row>
     <row r="232" spans="1:18" x14ac:dyDescent="0.4">
@@ -11342,7 +11347,7 @@
         <v>681</v>
       </c>
       <c r="B232" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C232">
         <v>598</v>
@@ -11363,7 +11368,7 @@
         <v>33</v>
       </c>
       <c r="R232" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="233" spans="1:18" x14ac:dyDescent="0.4">
@@ -11371,7 +11376,7 @@
         <v>682</v>
       </c>
       <c r="B233" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C233">
         <v>598</v>
@@ -11392,7 +11397,7 @@
         <v>20</v>
       </c>
       <c r="R233" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
     </row>
     <row r="234" spans="1:18" x14ac:dyDescent="0.4">
@@ -11400,7 +11405,7 @@
         <v>683</v>
       </c>
       <c r="B234" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C234">
         <v>598</v>
@@ -11421,7 +11426,7 @@
         <v>20</v>
       </c>
       <c r="R234" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
     </row>
     <row r="235" spans="1:18" x14ac:dyDescent="0.4">
@@ -11429,7 +11434,7 @@
         <v>684</v>
       </c>
       <c r="B235" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C235">
         <v>598</v>
@@ -11450,7 +11455,7 @@
         <v>20</v>
       </c>
       <c r="R235" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
     </row>
     <row r="236" spans="1:18" x14ac:dyDescent="0.4">
@@ -11458,7 +11463,7 @@
         <v>685</v>
       </c>
       <c r="B236" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C236">
         <v>598</v>
@@ -11479,7 +11484,7 @@
         <v>20</v>
       </c>
       <c r="R236" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
     </row>
     <row r="237" spans="1:18" x14ac:dyDescent="0.4">
@@ -11487,7 +11492,7 @@
         <v>686</v>
       </c>
       <c r="B237" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C237">
         <v>598</v>
@@ -11508,7 +11513,7 @@
         <v>33</v>
       </c>
       <c r="R237" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
     </row>
     <row r="238" spans="1:18" x14ac:dyDescent="0.4">
@@ -11516,7 +11521,7 @@
         <v>687</v>
       </c>
       <c r="B238" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C238">
         <v>598</v>
@@ -11528,7 +11533,7 @@
         <v>103</v>
       </c>
       <c r="F238" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="G238" t="s">
         <v>76</v>
@@ -11537,7 +11542,7 @@
         <v>20</v>
       </c>
       <c r="R238" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="239" spans="1:18" x14ac:dyDescent="0.4">
@@ -11545,7 +11550,7 @@
         <v>691</v>
       </c>
       <c r="B239" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C239">
         <v>600</v>
@@ -11569,7 +11574,7 @@
         <v>41</v>
       </c>
       <c r="R239" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
     </row>
     <row r="240" spans="1:18" x14ac:dyDescent="0.4">
@@ -11577,7 +11582,7 @@
         <v>692</v>
       </c>
       <c r="B240" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C240">
         <v>600</v>
@@ -11601,7 +11606,7 @@
         <v>40</v>
       </c>
       <c r="R240" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
     </row>
     <row r="241" spans="1:18" x14ac:dyDescent="0.4">
@@ -11609,7 +11614,7 @@
         <v>694</v>
       </c>
       <c r="B241" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C241">
         <v>604</v>
@@ -11627,16 +11632,16 @@
         <v>103</v>
       </c>
       <c r="H241" t="s">
+        <v>346</v>
+      </c>
+      <c r="I241" t="s">
+        <v>20</v>
+      </c>
+      <c r="J241" t="s">
         <v>347</v>
       </c>
-      <c r="I241" t="s">
-        <v>20</v>
-      </c>
-      <c r="J241" t="s">
-        <v>348</v>
-      </c>
       <c r="R241" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
     </row>
     <row r="242" spans="1:18" x14ac:dyDescent="0.4">
@@ -11644,7 +11649,7 @@
         <v>715</v>
       </c>
       <c r="B242" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C242">
         <v>609</v>
@@ -11680,7 +11685,7 @@
         <v>27</v>
       </c>
       <c r="R242" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
     </row>
     <row r="243" spans="1:18" x14ac:dyDescent="0.4">
@@ -11688,7 +11693,7 @@
         <v>716</v>
       </c>
       <c r="B243" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C243">
         <v>609</v>
@@ -11727,7 +11732,7 @@
         <v>27</v>
       </c>
       <c r="R243" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="244" spans="1:18" x14ac:dyDescent="0.4">
@@ -11735,7 +11740,7 @@
         <v>717</v>
       </c>
       <c r="B244" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C244">
         <v>609</v>
@@ -11771,7 +11776,7 @@
         <v>27</v>
       </c>
       <c r="R244" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
     </row>
     <row r="245" spans="1:18" x14ac:dyDescent="0.4">
@@ -11779,7 +11784,7 @@
         <v>722</v>
       </c>
       <c r="B245" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C245">
         <v>610</v>
@@ -11794,7 +11799,7 @@
         <v>45</v>
       </c>
       <c r="G245" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H245" t="s">
         <v>57</v>
@@ -11803,7 +11808,7 @@
         <v>20</v>
       </c>
       <c r="R245" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="246" spans="1:18" x14ac:dyDescent="0.4">
@@ -11811,7 +11816,7 @@
         <v>723</v>
       </c>
       <c r="B246" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C246">
         <v>610</v>
@@ -11826,7 +11831,7 @@
         <v>51</v>
       </c>
       <c r="G246" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H246" t="s">
         <v>57</v>
@@ -11835,7 +11840,7 @@
         <v>33</v>
       </c>
       <c r="R246" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
     </row>
     <row r="247" spans="1:18" x14ac:dyDescent="0.4">
@@ -11843,7 +11848,7 @@
         <v>725</v>
       </c>
       <c r="B247" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C247">
         <v>611</v>
@@ -11858,7 +11863,7 @@
         <v>55</v>
       </c>
       <c r="G247" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H247" t="s">
         <v>57</v>
@@ -11867,7 +11872,7 @@
         <v>20</v>
       </c>
       <c r="R247" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
     </row>
     <row r="248" spans="1:18" x14ac:dyDescent="0.4">
@@ -11875,7 +11880,7 @@
         <v>726</v>
       </c>
       <c r="B248" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C248">
         <v>611</v>
@@ -11890,7 +11895,7 @@
         <v>36</v>
       </c>
       <c r="G248" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H248" t="s">
         <v>57</v>
@@ -11899,7 +11904,7 @@
         <v>20</v>
       </c>
       <c r="R248" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
     </row>
     <row r="249" spans="1:18" x14ac:dyDescent="0.4">
@@ -11907,7 +11912,7 @@
         <v>727</v>
       </c>
       <c r="B249" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C249">
         <v>611</v>
@@ -11922,7 +11927,7 @@
         <v>45</v>
       </c>
       <c r="G249" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H249" t="s">
         <v>57</v>
@@ -11931,7 +11936,7 @@
         <v>20</v>
       </c>
       <c r="R249" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
     </row>
     <row r="250" spans="1:18" x14ac:dyDescent="0.4">
@@ -11939,7 +11944,7 @@
         <v>728</v>
       </c>
       <c r="B250" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C250">
         <v>611</v>
@@ -11954,7 +11959,7 @@
         <v>55</v>
       </c>
       <c r="G250" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H250" t="s">
         <v>57</v>
@@ -11963,7 +11968,7 @@
         <v>20</v>
       </c>
       <c r="R250" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
     </row>
     <row r="251" spans="1:18" x14ac:dyDescent="0.4">
@@ -11971,7 +11976,7 @@
         <v>729</v>
       </c>
       <c r="B251" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C251">
         <v>611</v>
@@ -11986,7 +11991,7 @@
         <v>51</v>
       </c>
       <c r="G251" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H251" t="s">
         <v>57</v>
@@ -11995,7 +12000,7 @@
         <v>20</v>
       </c>
       <c r="R251" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
     </row>
     <row r="252" spans="1:18" x14ac:dyDescent="0.4">
@@ -12003,7 +12008,7 @@
         <v>731</v>
       </c>
       <c r="B252" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C252">
         <v>611</v>
@@ -12036,7 +12041,7 @@
         <v>63</v>
       </c>
       <c r="R252" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
     </row>
     <row r="253" spans="1:18" x14ac:dyDescent="0.4">
@@ -12044,7 +12049,7 @@
         <v>734</v>
       </c>
       <c r="B253" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C253">
         <v>612</v>
@@ -12068,7 +12073,7 @@
         <v>20</v>
       </c>
       <c r="R253" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
     </row>
     <row r="254" spans="1:18" x14ac:dyDescent="0.4">
@@ -12076,7 +12081,7 @@
         <v>735</v>
       </c>
       <c r="B254" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C254">
         <v>612</v>
@@ -12100,7 +12105,7 @@
         <v>20</v>
       </c>
       <c r="R254" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
     </row>
     <row r="255" spans="1:18" x14ac:dyDescent="0.4">
@@ -12108,7 +12113,7 @@
         <v>736</v>
       </c>
       <c r="B255" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C255">
         <v>612</v>
@@ -12141,7 +12146,7 @@
         <v>27</v>
       </c>
       <c r="R255" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
     </row>
     <row r="256" spans="1:18" x14ac:dyDescent="0.4">
@@ -12149,7 +12154,7 @@
         <v>737</v>
       </c>
       <c r="B256" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C256">
         <v>613</v>
@@ -12170,7 +12175,7 @@
         <v>20</v>
       </c>
       <c r="R256" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
     </row>
     <row r="257" spans="1:18" x14ac:dyDescent="0.4">
@@ -12178,7 +12183,7 @@
         <v>738</v>
       </c>
       <c r="B257" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C257">
         <v>613</v>
@@ -12193,7 +12198,7 @@
         <v>51</v>
       </c>
       <c r="G257" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H257" t="s">
         <v>57</v>
@@ -12202,7 +12207,7 @@
         <v>20</v>
       </c>
       <c r="R257" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
     </row>
     <row r="258" spans="1:18" x14ac:dyDescent="0.4">
@@ -12210,7 +12215,7 @@
         <v>740</v>
       </c>
       <c r="B258" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C258">
         <v>616</v>
@@ -12237,7 +12242,7 @@
         <v>40</v>
       </c>
       <c r="R258" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
     </row>
     <row r="259" spans="1:18" x14ac:dyDescent="0.4">
@@ -12245,7 +12250,7 @@
         <v>742</v>
       </c>
       <c r="B259" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C259">
         <v>621</v>
@@ -12257,10 +12262,10 @@
         <v>520</v>
       </c>
       <c r="F259" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="G259" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H259" t="s">
         <v>57</v>
@@ -12269,7 +12274,7 @@
         <v>20</v>
       </c>
       <c r="R259" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
     </row>
     <row r="260" spans="1:18" x14ac:dyDescent="0.4">
@@ -12277,7 +12282,7 @@
         <v>744</v>
       </c>
       <c r="B260" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C260">
         <v>621</v>
@@ -12310,7 +12315,7 @@
         <v>80</v>
       </c>
       <c r="R260" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
     </row>
     <row r="261" spans="1:18" x14ac:dyDescent="0.4">
@@ -12318,7 +12323,7 @@
         <v>747</v>
       </c>
       <c r="B261" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C261">
         <v>623</v>
@@ -12336,7 +12341,7 @@
         <v>85</v>
       </c>
       <c r="H261" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="I261" t="s">
         <v>33</v>
@@ -12345,7 +12350,7 @@
         <v>27</v>
       </c>
       <c r="R261" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="262" spans="1:18" x14ac:dyDescent="0.4">
@@ -12353,7 +12358,7 @@
         <v>748</v>
       </c>
       <c r="B262" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C262">
         <v>623</v>
@@ -12368,7 +12373,7 @@
         <v>51</v>
       </c>
       <c r="G262" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H262" t="s">
         <v>57</v>
@@ -12377,7 +12382,7 @@
         <v>20</v>
       </c>
       <c r="R262" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
     </row>
     <row r="263" spans="1:18" x14ac:dyDescent="0.4">
@@ -12385,7 +12390,7 @@
         <v>764</v>
       </c>
       <c r="B263" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C263">
         <v>651</v>
@@ -12400,13 +12405,13 @@
         <v>36</v>
       </c>
       <c r="G263" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="I263" t="s">
         <v>20</v>
       </c>
       <c r="R263" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="264" spans="1:18" x14ac:dyDescent="0.4">
@@ -12414,7 +12419,7 @@
         <v>765</v>
       </c>
       <c r="B264" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C264">
         <v>651</v>
@@ -12435,7 +12440,7 @@
         <v>20</v>
       </c>
       <c r="R264" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="265" spans="1:18" x14ac:dyDescent="0.4">
@@ -12443,7 +12448,7 @@
         <v>767</v>
       </c>
       <c r="B265" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C265">
         <v>625</v>
@@ -12467,7 +12472,7 @@
         <v>21</v>
       </c>
       <c r="R265" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
     </row>
     <row r="266" spans="1:18" x14ac:dyDescent="0.4">
@@ -12475,7 +12480,7 @@
         <v>786</v>
       </c>
       <c r="B266" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C266">
         <v>657</v>
@@ -12490,13 +12495,13 @@
         <v>36</v>
       </c>
       <c r="G266" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="I266" t="s">
         <v>33</v>
       </c>
       <c r="R266" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="267" spans="1:18" x14ac:dyDescent="0.4">
@@ -12504,7 +12509,7 @@
         <v>796</v>
       </c>
       <c r="B267" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C267">
         <v>662</v>
@@ -12528,7 +12533,7 @@
         <v>229</v>
       </c>
       <c r="R267" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="268" spans="1:18" x14ac:dyDescent="0.4">
@@ -12536,7 +12541,7 @@
         <v>797</v>
       </c>
       <c r="B268" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C268">
         <v>664</v>
@@ -12557,7 +12562,7 @@
         <v>20</v>
       </c>
       <c r="R268" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="269" spans="1:18" x14ac:dyDescent="0.4">
@@ -12565,7 +12570,7 @@
         <v>798</v>
       </c>
       <c r="B269" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C269">
         <v>667</v>
@@ -12577,7 +12582,7 @@
         <v>4250</v>
       </c>
       <c r="F269" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="G269" t="s">
         <v>85</v>
@@ -12586,10 +12591,10 @@
         <v>20</v>
       </c>
       <c r="J269" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="R269" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
     </row>
     <row r="270" spans="1:18" x14ac:dyDescent="0.4">
@@ -12597,7 +12602,7 @@
         <v>799</v>
       </c>
       <c r="B270" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C270">
         <v>667</v>
@@ -12609,7 +12614,7 @@
         <v>4250</v>
       </c>
       <c r="F270" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="G270" t="s">
         <v>85</v>
@@ -12618,10 +12623,10 @@
         <v>20</v>
       </c>
       <c r="J270" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="R270" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
     </row>
     <row r="271" spans="1:18" x14ac:dyDescent="0.4">
@@ -12629,7 +12634,7 @@
         <v>803</v>
       </c>
       <c r="B271" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C271">
         <v>668</v>
@@ -12644,16 +12649,16 @@
         <v>65</v>
       </c>
       <c r="G271" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H271" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="I271" t="s">
         <v>66</v>
       </c>
       <c r="R271" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
     </row>
     <row r="272" spans="1:18" x14ac:dyDescent="0.4">
@@ -12661,7 +12666,7 @@
         <v>804</v>
       </c>
       <c r="B272" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C272">
         <v>672</v>
@@ -12682,7 +12687,7 @@
         <v>20</v>
       </c>
       <c r="R272" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
     </row>
     <row r="273" spans="1:18" x14ac:dyDescent="0.4">
@@ -12690,7 +12695,7 @@
         <v>805</v>
       </c>
       <c r="B273" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C273">
         <v>672</v>
@@ -12708,7 +12713,7 @@
         <v>268</v>
       </c>
       <c r="H273" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="I273" t="s">
         <v>20</v>
@@ -12717,7 +12722,7 @@
         <v>64</v>
       </c>
       <c r="R273" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
     </row>
     <row r="274" spans="1:18" x14ac:dyDescent="0.4">
@@ -12725,7 +12730,7 @@
         <v>810</v>
       </c>
       <c r="B274" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C274">
         <v>685</v>
@@ -12743,7 +12748,7 @@
         <v>268</v>
       </c>
       <c r="H274" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="I274" t="s">
         <v>20</v>
@@ -12758,7 +12763,7 @@
         <v>229</v>
       </c>
       <c r="R274" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
     </row>
     <row r="275" spans="1:18" x14ac:dyDescent="0.4">
@@ -12766,7 +12771,7 @@
         <v>812</v>
       </c>
       <c r="B275" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C275">
         <v>692</v>
@@ -12784,13 +12789,13 @@
         <v>103</v>
       </c>
       <c r="H275" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="I275" t="s">
         <v>33</v>
       </c>
       <c r="R275" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
     </row>
     <row r="276" spans="1:18" x14ac:dyDescent="0.4">
@@ -12798,7 +12803,7 @@
         <v>813</v>
       </c>
       <c r="B276" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C276">
         <v>692</v>
@@ -12819,7 +12824,7 @@
         <v>20</v>
       </c>
       <c r="R276" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
     </row>
     <row r="277" spans="1:18" x14ac:dyDescent="0.4">
@@ -12827,7 +12832,7 @@
         <v>830</v>
       </c>
       <c r="B277" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C277">
         <v>705</v>
@@ -12848,7 +12853,7 @@
         <v>20</v>
       </c>
       <c r="R277" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="278" spans="1:18" x14ac:dyDescent="0.4">
@@ -12856,7 +12861,7 @@
         <v>833</v>
       </c>
       <c r="B278" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C278">
         <v>703</v>
@@ -12874,7 +12879,7 @@
         <v>85</v>
       </c>
       <c r="H278" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="I278" t="s">
         <v>33</v>
@@ -12886,7 +12891,7 @@
         <v>42</v>
       </c>
       <c r="R278" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="279" spans="1:18" x14ac:dyDescent="0.4">
@@ -12894,7 +12899,7 @@
         <v>834</v>
       </c>
       <c r="B279" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C279">
         <v>703</v>
@@ -12912,7 +12917,7 @@
         <v>85</v>
       </c>
       <c r="H279" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="I279" t="s">
         <v>20</v>
@@ -12924,7 +12929,7 @@
         <v>80</v>
       </c>
       <c r="R279" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
     </row>
     <row r="280" spans="1:18" x14ac:dyDescent="0.4">
@@ -12932,7 +12937,7 @@
         <v>838</v>
       </c>
       <c r="B280" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C280">
         <v>704</v>
@@ -12950,7 +12955,7 @@
         <v>48</v>
       </c>
       <c r="H280" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="I280" t="s">
         <v>20</v>
@@ -12959,7 +12964,7 @@
         <v>175</v>
       </c>
       <c r="R280" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
     </row>
     <row r="281" spans="1:18" x14ac:dyDescent="0.4">
@@ -12967,7 +12972,7 @@
         <v>839</v>
       </c>
       <c r="B281" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C281">
         <v>704</v>
@@ -12985,7 +12990,7 @@
         <v>48</v>
       </c>
       <c r="H281" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="I281" t="s">
         <v>20</v>
@@ -12997,7 +13002,7 @@
         <v>41</v>
       </c>
       <c r="R281" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="282" spans="1:18" x14ac:dyDescent="0.4">
@@ -13005,7 +13010,7 @@
         <v>841</v>
       </c>
       <c r="B282" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C282">
         <v>704</v>
@@ -13023,7 +13028,7 @@
         <v>44</v>
       </c>
       <c r="H282" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="I282" t="s">
         <v>20</v>
@@ -13032,7 +13037,7 @@
         <v>41</v>
       </c>
       <c r="R282" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
     </row>
     <row r="283" spans="1:18" x14ac:dyDescent="0.4">
@@ -13040,7 +13045,7 @@
         <v>842</v>
       </c>
       <c r="B283" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C283">
         <v>704</v>
@@ -13058,7 +13063,7 @@
         <v>44</v>
       </c>
       <c r="H283" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="I283" t="s">
         <v>20</v>
@@ -13067,7 +13072,7 @@
         <v>40</v>
       </c>
       <c r="R283" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
     </row>
     <row r="284" spans="1:18" x14ac:dyDescent="0.4">
@@ -13075,7 +13080,7 @@
         <v>844</v>
       </c>
       <c r="B284" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C284">
         <v>704</v>
@@ -13093,13 +13098,13 @@
         <v>85</v>
       </c>
       <c r="H284" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="I284" t="s">
         <v>20</v>
       </c>
       <c r="R284" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="285" spans="1:18" x14ac:dyDescent="0.4">
@@ -13107,7 +13112,7 @@
         <v>845</v>
       </c>
       <c r="B285" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C285">
         <v>704</v>
@@ -13128,7 +13133,7 @@
         <v>20</v>
       </c>
       <c r="R285" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="286" spans="1:18" x14ac:dyDescent="0.4">
@@ -13136,7 +13141,7 @@
         <v>848</v>
       </c>
       <c r="B286" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C286">
         <v>704</v>
@@ -13154,13 +13159,13 @@
         <v>44</v>
       </c>
       <c r="H286" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="I286" t="s">
         <v>20</v>
       </c>
       <c r="R286" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="287" spans="1:18" x14ac:dyDescent="0.4">
@@ -13168,7 +13173,7 @@
         <v>849</v>
       </c>
       <c r="B287" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C287">
         <v>704</v>
@@ -13186,13 +13191,13 @@
         <v>44</v>
       </c>
       <c r="H287" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="I287" t="s">
         <v>20</v>
       </c>
       <c r="R287" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="288" spans="1:18" x14ac:dyDescent="0.4">
@@ -13200,7 +13205,7 @@
         <v>850</v>
       </c>
       <c r="B288" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C288">
         <v>704</v>
@@ -13218,7 +13223,7 @@
         <v>85</v>
       </c>
       <c r="H288" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="I288" t="s">
         <v>33</v>
@@ -13233,7 +13238,7 @@
         <v>27</v>
       </c>
       <c r="R288" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
     </row>
     <row r="289" spans="1:18" x14ac:dyDescent="0.4">
@@ -13241,7 +13246,7 @@
         <v>855</v>
       </c>
       <c r="B289" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C289">
         <v>705</v>
@@ -13262,7 +13267,7 @@
         <v>20</v>
       </c>
       <c r="R289" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
     </row>
     <row r="290" spans="1:18" x14ac:dyDescent="0.4">
@@ -13270,7 +13275,7 @@
         <v>857</v>
       </c>
       <c r="B290" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C290">
         <v>706</v>
@@ -13291,7 +13296,7 @@
         <v>20</v>
       </c>
       <c r="R290" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="291" spans="1:18" x14ac:dyDescent="0.4">
@@ -13299,7 +13304,7 @@
         <v>859</v>
       </c>
       <c r="B291" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C291">
         <v>706</v>
@@ -13320,7 +13325,7 @@
         <v>20</v>
       </c>
       <c r="R291" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="292" spans="1:18" x14ac:dyDescent="0.4">
@@ -13328,7 +13333,7 @@
         <v>861</v>
       </c>
       <c r="B292" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C292">
         <v>706</v>
@@ -13358,7 +13363,7 @@
         <v>27</v>
       </c>
       <c r="R292" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="293" spans="1:18" x14ac:dyDescent="0.4">
@@ -13366,7 +13371,7 @@
         <v>868</v>
       </c>
       <c r="B293" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C293">
         <v>706</v>
@@ -13387,7 +13392,7 @@
         <v>20</v>
       </c>
       <c r="R293" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="294" spans="1:18" x14ac:dyDescent="0.4">
@@ -13395,7 +13400,7 @@
         <v>870</v>
       </c>
       <c r="B294" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C294">
         <v>706</v>
@@ -13413,7 +13418,7 @@
         <v>85</v>
       </c>
       <c r="H294" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="I294" t="s">
         <v>20</v>
@@ -13425,7 +13430,7 @@
         <v>80</v>
       </c>
       <c r="R294" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
     </row>
     <row r="295" spans="1:18" x14ac:dyDescent="0.4">
@@ -13433,7 +13438,7 @@
         <v>871</v>
       </c>
       <c r="B295" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C295">
         <v>707</v>
@@ -13454,7 +13459,7 @@
         <v>20</v>
       </c>
       <c r="R295" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
     </row>
     <row r="296" spans="1:18" x14ac:dyDescent="0.4">
@@ -13462,7 +13467,7 @@
         <v>875</v>
       </c>
       <c r="B296" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C296">
         <v>711</v>
@@ -13480,7 +13485,7 @@
         <v>85</v>
       </c>
       <c r="H296" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="I296" t="s">
         <v>20</v>
@@ -13489,7 +13494,7 @@
         <v>28</v>
       </c>
       <c r="R296" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
     </row>
     <row r="297" spans="1:18" x14ac:dyDescent="0.4">
@@ -13497,7 +13502,7 @@
         <v>885</v>
       </c>
       <c r="B297" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C297">
         <v>714</v>
@@ -13518,7 +13523,7 @@
         <v>33</v>
       </c>
       <c r="R297" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
     </row>
     <row r="298" spans="1:18" x14ac:dyDescent="0.4">
@@ -13526,7 +13531,7 @@
         <v>887</v>
       </c>
       <c r="B298" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C298">
         <v>717</v>
@@ -13547,7 +13552,7 @@
         <v>20</v>
       </c>
       <c r="R298" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
     </row>
     <row r="299" spans="1:18" x14ac:dyDescent="0.4">
@@ -13555,7 +13560,7 @@
         <v>901</v>
       </c>
       <c r="B299" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C299">
         <v>723</v>
@@ -13576,7 +13581,7 @@
         <v>20</v>
       </c>
       <c r="R299" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
     </row>
     <row r="300" spans="1:18" x14ac:dyDescent="0.4">
@@ -13584,7 +13589,7 @@
         <v>902</v>
       </c>
       <c r="B300" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C300">
         <v>729</v>
@@ -13596,7 +13601,7 @@
         <v>145</v>
       </c>
       <c r="F300" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="G300" t="s">
         <v>103</v>
@@ -13605,7 +13610,7 @@
         <v>20</v>
       </c>
       <c r="R300" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
     </row>
     <row r="301" spans="1:18" x14ac:dyDescent="0.4">
@@ -13613,7 +13618,7 @@
         <v>903</v>
       </c>
       <c r="B301" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C301">
         <v>731</v>
@@ -13637,7 +13642,7 @@
         <v>42</v>
       </c>
       <c r="R301" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
     </row>
     <row r="302" spans="1:18" x14ac:dyDescent="0.4">
@@ -13645,7 +13650,7 @@
         <v>904</v>
       </c>
       <c r="B302" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C302">
         <v>732</v>
@@ -13669,7 +13674,7 @@
         <v>64</v>
       </c>
       <c r="R302" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="303" spans="1:18" x14ac:dyDescent="0.4">
@@ -13677,7 +13682,7 @@
         <v>906</v>
       </c>
       <c r="B303" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C303">
         <v>735</v>
@@ -13698,7 +13703,7 @@
         <v>20</v>
       </c>
       <c r="R303" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="304" spans="1:18" x14ac:dyDescent="0.4">
@@ -13706,7 +13711,7 @@
         <v>907</v>
       </c>
       <c r="B304" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C304">
         <v>736</v>
@@ -13727,7 +13732,7 @@
         <v>20</v>
       </c>
       <c r="R304" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
     </row>
     <row r="305" spans="1:18" x14ac:dyDescent="0.4">
@@ -13735,7 +13740,7 @@
         <v>908</v>
       </c>
       <c r="B305" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C305">
         <v>736</v>
@@ -13756,7 +13761,7 @@
         <v>20</v>
       </c>
       <c r="R305" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="306" spans="1:18" x14ac:dyDescent="0.4">
@@ -13764,7 +13769,7 @@
         <v>909</v>
       </c>
       <c r="B306" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C306">
         <v>737</v>
@@ -13785,7 +13790,7 @@
         <v>20</v>
       </c>
       <c r="R306" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="307" spans="1:18" x14ac:dyDescent="0.4">
@@ -13793,7 +13798,7 @@
         <v>914</v>
       </c>
       <c r="B307" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C307">
         <v>747</v>
@@ -13814,7 +13819,7 @@
         <v>20</v>
       </c>
       <c r="R307" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
     </row>
     <row r="308" spans="1:18" x14ac:dyDescent="0.4">
@@ -13822,7 +13827,7 @@
         <v>917</v>
       </c>
       <c r="B308" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C308">
         <v>754</v>
@@ -13840,13 +13845,13 @@
         <v>268</v>
       </c>
       <c r="H308" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="I308" t="s">
         <v>20</v>
       </c>
       <c r="R308" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
     </row>
     <row r="309" spans="1:18" x14ac:dyDescent="0.4">
@@ -13854,7 +13859,7 @@
         <v>924</v>
       </c>
       <c r="B309" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C309">
         <v>761</v>
@@ -13881,7 +13886,7 @@
         <v>40</v>
       </c>
       <c r="R309" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="310" spans="1:18" x14ac:dyDescent="0.4">
@@ -13889,7 +13894,7 @@
         <v>935</v>
       </c>
       <c r="B310" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C310">
         <v>774</v>
@@ -13907,7 +13912,7 @@
         <v>85</v>
       </c>
       <c r="H310" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="I310" t="s">
         <v>33</v>
@@ -13916,7 +13921,7 @@
         <v>21</v>
       </c>
       <c r="R310" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="311" spans="1:18" x14ac:dyDescent="0.4">
@@ -13924,7 +13929,7 @@
         <v>944</v>
       </c>
       <c r="B311" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C311">
         <v>795</v>
@@ -13948,7 +13953,7 @@
         <v>80</v>
       </c>
       <c r="R311" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="312" spans="1:18" x14ac:dyDescent="0.4">
@@ -13956,7 +13961,7 @@
         <v>947</v>
       </c>
       <c r="B312" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C312">
         <v>802</v>
@@ -13977,7 +13982,7 @@
         <v>20</v>
       </c>
       <c r="R312" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="313" spans="1:18" x14ac:dyDescent="0.4">
@@ -13985,7 +13990,7 @@
         <v>948</v>
       </c>
       <c r="B313" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C313">
         <v>802</v>
@@ -14006,7 +14011,7 @@
         <v>33</v>
       </c>
       <c r="R313" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
     </row>
     <row r="314" spans="1:18" x14ac:dyDescent="0.4">
@@ -14014,7 +14019,7 @@
         <v>954</v>
       </c>
       <c r="B314" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C314">
         <v>805</v>
@@ -14029,13 +14034,13 @@
         <v>55</v>
       </c>
       <c r="G314" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="I314" t="s">
         <v>33</v>
       </c>
       <c r="R314" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
     </row>
     <row r="315" spans="1:18" x14ac:dyDescent="0.4">
@@ -14043,7 +14048,7 @@
         <v>955</v>
       </c>
       <c r="B315" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C315">
         <v>805</v>
@@ -14058,13 +14063,13 @@
         <v>55</v>
       </c>
       <c r="G315" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="I315" t="s">
         <v>33</v>
       </c>
       <c r="R315" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
     </row>
     <row r="316" spans="1:18" x14ac:dyDescent="0.4">
@@ -14072,7 +14077,7 @@
         <v>960</v>
       </c>
       <c r="B316" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C316">
         <v>808</v>
@@ -14093,7 +14098,7 @@
         <v>20</v>
       </c>
       <c r="R316" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
     </row>
     <row r="317" spans="1:18" x14ac:dyDescent="0.4">
@@ -14101,7 +14106,7 @@
         <v>961</v>
       </c>
       <c r="B317" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C317">
         <v>808</v>
@@ -14122,7 +14127,7 @@
         <v>20</v>
       </c>
       <c r="R317" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="318" spans="1:18" x14ac:dyDescent="0.4">
@@ -14130,7 +14135,7 @@
         <v>966</v>
       </c>
       <c r="B318" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C318">
         <v>808</v>
@@ -14145,13 +14150,13 @@
         <v>51</v>
       </c>
       <c r="G318" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="I318" t="s">
         <v>20</v>
       </c>
       <c r="R318" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
     </row>
     <row r="319" spans="1:18" x14ac:dyDescent="0.4">
@@ -14159,7 +14164,7 @@
         <v>967</v>
       </c>
       <c r="B319" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C319">
         <v>808</v>
@@ -14174,13 +14179,13 @@
         <v>45</v>
       </c>
       <c r="G319" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="I319" t="s">
         <v>20</v>
       </c>
       <c r="R319" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
     </row>
     <row r="320" spans="1:18" x14ac:dyDescent="0.4">
@@ -14188,7 +14193,7 @@
         <v>969</v>
       </c>
       <c r="B320" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C320">
         <v>808</v>
@@ -14203,13 +14208,13 @@
         <v>36</v>
       </c>
       <c r="G320" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="I320" t="s">
         <v>20</v>
       </c>
       <c r="R320" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
     </row>
     <row r="321" spans="1:18" x14ac:dyDescent="0.4">
@@ -14217,7 +14222,7 @@
         <v>970</v>
       </c>
       <c r="B321" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C321">
         <v>808</v>
@@ -14232,13 +14237,13 @@
         <v>55</v>
       </c>
       <c r="G321" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="I321" t="s">
         <v>20</v>
       </c>
       <c r="R321" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
     </row>
     <row r="322" spans="1:18" x14ac:dyDescent="0.4">
@@ -14246,7 +14251,7 @@
         <v>971</v>
       </c>
       <c r="B322" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C322">
         <v>809</v>
@@ -14261,13 +14266,13 @@
         <v>36</v>
       </c>
       <c r="G322" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="I322" t="s">
         <v>20</v>
       </c>
       <c r="R322" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
     </row>
     <row r="323" spans="1:18" x14ac:dyDescent="0.4">
@@ -14275,7 +14280,7 @@
         <v>976</v>
       </c>
       <c r="B323" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C323">
         <v>813</v>
@@ -14296,7 +14301,7 @@
         <v>20</v>
       </c>
       <c r="R323" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
     </row>
     <row r="324" spans="1:18" x14ac:dyDescent="0.4">
@@ -14304,7 +14309,7 @@
         <v>977</v>
       </c>
       <c r="B324" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C324">
         <v>814</v>
@@ -14319,13 +14324,13 @@
         <v>55</v>
       </c>
       <c r="G324" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="I324" t="s">
         <v>20</v>
       </c>
       <c r="R324" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
     </row>
     <row r="325" spans="1:18" x14ac:dyDescent="0.4">
@@ -14333,7 +14338,7 @@
         <v>981</v>
       </c>
       <c r="B325" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C325">
         <v>817</v>
@@ -14351,13 +14356,13 @@
         <v>268</v>
       </c>
       <c r="H325" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="I325" t="s">
         <v>20</v>
       </c>
       <c r="R325" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
     </row>
     <row r="326" spans="1:18" x14ac:dyDescent="0.4">
@@ -14365,7 +14370,7 @@
         <v>983</v>
       </c>
       <c r="B326" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C326">
         <v>824</v>
@@ -14383,7 +14388,7 @@
         <v>85</v>
       </c>
       <c r="H326" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="I326" t="s">
         <v>33</v>
@@ -14404,7 +14409,7 @@
         <v>229</v>
       </c>
       <c r="R326" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
     </row>
     <row r="327" spans="1:18" x14ac:dyDescent="0.4">
@@ -14412,7 +14417,7 @@
         <v>984</v>
       </c>
       <c r="B327" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C327">
         <v>825</v>
@@ -14433,7 +14438,7 @@
         <v>20</v>
       </c>
       <c r="R327" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
     </row>
     <row r="328" spans="1:18" x14ac:dyDescent="0.4">
@@ -14441,7 +14446,7 @@
         <v>987</v>
       </c>
       <c r="B328" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C328">
         <v>826</v>
@@ -14453,7 +14458,7 @@
         <v>194</v>
       </c>
       <c r="F328" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="G328" t="s">
         <v>103</v>
@@ -14477,7 +14482,7 @@
         <v>42</v>
       </c>
       <c r="R328" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
     </row>
     <row r="329" spans="1:18" x14ac:dyDescent="0.4">
@@ -14485,7 +14490,7 @@
         <v>988</v>
       </c>
       <c r="B329" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C329">
         <v>826</v>
@@ -14518,7 +14523,7 @@
         <v>41</v>
       </c>
       <c r="R329" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
     </row>
     <row r="330" spans="1:18" x14ac:dyDescent="0.4">
@@ -14526,7 +14531,7 @@
         <v>996</v>
       </c>
       <c r="B330" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C330">
         <v>829</v>
@@ -14556,7 +14561,7 @@
         <v>80</v>
       </c>
       <c r="R330" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
     </row>
     <row r="331" spans="1:18" x14ac:dyDescent="0.4">
@@ -14564,7 +14569,7 @@
         <v>997</v>
       </c>
       <c r="B331" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C331">
         <v>830</v>
@@ -14576,13 +14581,13 @@
         <v>800</v>
       </c>
       <c r="F331" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="G331" t="s">
         <v>85</v>
       </c>
       <c r="H331" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="I331" t="s">
         <v>33</v>
@@ -14606,7 +14611,7 @@
         <v>229</v>
       </c>
       <c r="R331" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
     </row>
     <row r="332" spans="1:18" x14ac:dyDescent="0.4">
@@ -14614,7 +14619,7 @@
         <v>1000</v>
       </c>
       <c r="B332" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C332">
         <v>831</v>
@@ -14629,7 +14634,7 @@
         <v>55</v>
       </c>
       <c r="G332" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="I332" t="s">
         <v>20</v>
@@ -14641,7 +14646,7 @@
         <v>80</v>
       </c>
       <c r="R332" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
     </row>
     <row r="333" spans="1:18" x14ac:dyDescent="0.4">
@@ -14649,7 +14654,7 @@
         <v>1003</v>
       </c>
       <c r="B333" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C333">
         <v>832</v>
@@ -14664,7 +14669,7 @@
         <v>62</v>
       </c>
       <c r="G333" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="I333" t="s">
         <v>33</v>
@@ -14685,7 +14690,7 @@
         <v>229</v>
       </c>
       <c r="R333" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
     </row>
     <row r="334" spans="1:18" x14ac:dyDescent="0.4">
@@ -14693,7 +14698,7 @@
         <v>1004</v>
       </c>
       <c r="B334" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C334">
         <v>832</v>
@@ -14726,7 +14731,7 @@
         <v>80</v>
       </c>
       <c r="R334" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
     </row>
     <row r="335" spans="1:18" x14ac:dyDescent="0.4">
@@ -14734,7 +14739,7 @@
         <v>1007</v>
       </c>
       <c r="B335" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C335">
         <v>834</v>
@@ -14752,7 +14757,7 @@
         <v>85</v>
       </c>
       <c r="H335" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="I335" t="s">
         <v>33</v>
@@ -14782,7 +14787,7 @@
         <v>63</v>
       </c>
       <c r="R335" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
     </row>
     <row r="336" spans="1:18" x14ac:dyDescent="0.4">
@@ -14790,7 +14795,7 @@
         <v>1009</v>
       </c>
       <c r="B336" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C336">
         <v>834</v>
@@ -14805,7 +14810,7 @@
         <v>45</v>
       </c>
       <c r="G336" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="I336" t="s">
         <v>20</v>
@@ -14826,7 +14831,7 @@
         <v>229</v>
       </c>
       <c r="R336" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="337" spans="1:18" x14ac:dyDescent="0.4">
@@ -14834,7 +14839,7 @@
         <v>1011</v>
       </c>
       <c r="B337" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C337">
         <v>835</v>
@@ -14849,10 +14854,10 @@
         <v>45</v>
       </c>
       <c r="G337" t="s">
+        <v>463</v>
+      </c>
+      <c r="I337" t="s">
         <v>464</v>
-      </c>
-      <c r="I337" t="s">
-        <v>465</v>
       </c>
       <c r="J337" t="s">
         <v>27</v>
@@ -14870,7 +14875,7 @@
         <v>229</v>
       </c>
       <c r="R337" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
     </row>
     <row r="338" spans="1:18" x14ac:dyDescent="0.4">
@@ -14878,7 +14883,7 @@
         <v>1012</v>
       </c>
       <c r="B338" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C338">
         <v>836</v>
@@ -14896,13 +14901,13 @@
         <v>85</v>
       </c>
       <c r="H338" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="I338" t="s">
         <v>20</v>
       </c>
       <c r="R338" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
     </row>
     <row r="339" spans="1:18" x14ac:dyDescent="0.4">
@@ -14910,7 +14915,7 @@
         <v>1013</v>
       </c>
       <c r="B339" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C339">
         <v>838</v>
@@ -14922,7 +14927,7 @@
         <v>186</v>
       </c>
       <c r="F339" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="G339" t="s">
         <v>103</v>
@@ -14946,7 +14951,7 @@
         <v>41</v>
       </c>
       <c r="R339" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
     </row>
     <row r="340" spans="1:18" x14ac:dyDescent="0.4">
@@ -14954,7 +14959,7 @@
         <v>1014</v>
       </c>
       <c r="B340" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C340">
         <v>838</v>
@@ -14966,7 +14971,7 @@
         <v>185</v>
       </c>
       <c r="F340" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="G340" t="s">
         <v>103</v>
@@ -14993,7 +14998,7 @@
         <v>41</v>
       </c>
       <c r="R340" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
     </row>
     <row r="341" spans="1:18" x14ac:dyDescent="0.4">
@@ -15001,7 +15006,7 @@
         <v>1032</v>
       </c>
       <c r="B341" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C341">
         <v>860</v>
@@ -15019,13 +15024,13 @@
         <v>85</v>
       </c>
       <c r="H341" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="I341" t="s">
         <v>33</v>
       </c>
       <c r="R341" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
     </row>
     <row r="342" spans="1:18" x14ac:dyDescent="0.4">
@@ -15033,7 +15038,7 @@
         <v>1033</v>
       </c>
       <c r="B342" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C342">
         <v>843</v>
@@ -15048,7 +15053,7 @@
         <v>45</v>
       </c>
       <c r="G342" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="I342" t="s">
         <v>20</v>
@@ -15069,7 +15074,7 @@
         <v>229</v>
       </c>
       <c r="R342" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="343" spans="1:18" x14ac:dyDescent="0.4">
@@ -15077,7 +15082,7 @@
         <v>1049</v>
       </c>
       <c r="B343" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C343">
         <v>846</v>
@@ -15095,7 +15100,7 @@
         <v>85</v>
       </c>
       <c r="H343" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="I343" t="s">
         <v>33</v>
@@ -15116,7 +15121,7 @@
         <v>229</v>
       </c>
       <c r="R343" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="344" spans="1:18" x14ac:dyDescent="0.4">
@@ -15124,7 +15129,7 @@
         <v>1058</v>
       </c>
       <c r="B344" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C344">
         <v>853</v>
@@ -15145,7 +15150,7 @@
         <v>66</v>
       </c>
       <c r="R344" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
     </row>
     <row r="345" spans="1:18" x14ac:dyDescent="0.4">
@@ -15153,7 +15158,7 @@
         <v>1059</v>
       </c>
       <c r="B345" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C345">
         <v>853</v>
@@ -15174,7 +15179,7 @@
         <v>66</v>
       </c>
       <c r="R345" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
     </row>
     <row r="346" spans="1:18" x14ac:dyDescent="0.4">
@@ -15182,7 +15187,7 @@
         <v>1060</v>
       </c>
       <c r="B346" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C346">
         <v>853</v>
@@ -15203,7 +15208,7 @@
         <v>66</v>
       </c>
       <c r="R346" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
     </row>
     <row r="347" spans="1:18" x14ac:dyDescent="0.4">
@@ -15211,7 +15216,7 @@
         <v>1066</v>
       </c>
       <c r="B347" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C347">
         <v>858</v>
@@ -15232,7 +15237,7 @@
         <v>20</v>
       </c>
       <c r="R347" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
     </row>
     <row r="348" spans="1:18" x14ac:dyDescent="0.4">
@@ -15240,7 +15245,7 @@
         <v>1070</v>
       </c>
       <c r="B348" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C348">
         <v>860</v>
@@ -15261,7 +15266,7 @@
         <v>20</v>
       </c>
       <c r="R348" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="349" spans="1:18" x14ac:dyDescent="0.4">
@@ -15269,7 +15274,7 @@
         <v>1076</v>
       </c>
       <c r="B349" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C349">
         <v>860</v>
@@ -15284,7 +15289,7 @@
         <v>51</v>
       </c>
       <c r="G349" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="I349" t="s">
         <v>20</v>
@@ -15305,7 +15310,7 @@
         <v>229</v>
       </c>
       <c r="R349" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
     </row>
     <row r="350" spans="1:18" x14ac:dyDescent="0.4">
@@ -15313,7 +15318,7 @@
         <v>1087</v>
       </c>
       <c r="B350" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C350">
         <v>864</v>
@@ -15328,7 +15333,7 @@
         <v>45</v>
       </c>
       <c r="G350" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="I350" t="s">
         <v>20</v>
@@ -15349,7 +15354,7 @@
         <v>229</v>
       </c>
       <c r="R350" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="351" spans="1:18" x14ac:dyDescent="0.4">
@@ -15357,7 +15362,7 @@
         <v>1088</v>
       </c>
       <c r="B351" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C351">
         <v>864</v>
@@ -15372,7 +15377,7 @@
         <v>55</v>
       </c>
       <c r="G351" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="I351" t="s">
         <v>20</v>
@@ -15393,7 +15398,7 @@
         <v>229</v>
       </c>
       <c r="R351" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="352" spans="1:18" x14ac:dyDescent="0.4">
@@ -15401,7 +15406,7 @@
         <v>1100</v>
       </c>
       <c r="B352" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C352">
         <v>866</v>
@@ -15422,7 +15427,7 @@
         <v>33</v>
       </c>
       <c r="R352" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
     </row>
     <row r="353" spans="1:18" x14ac:dyDescent="0.4">
@@ -15430,7 +15435,7 @@
         <v>1111</v>
       </c>
       <c r="B353" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C353">
         <v>866</v>
@@ -15454,7 +15459,7 @@
         <v>33</v>
       </c>
       <c r="R353" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="354" spans="1:18" x14ac:dyDescent="0.4">
@@ -15462,7 +15467,7 @@
         <v>1113</v>
       </c>
       <c r="B354" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C354">
         <v>866</v>
@@ -15486,7 +15491,7 @@
         <v>20</v>
       </c>
       <c r="R354" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
     </row>
     <row r="355" spans="1:18" x14ac:dyDescent="0.4">
@@ -15494,7 +15499,7 @@
         <v>1114</v>
       </c>
       <c r="B355" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C355">
         <v>866</v>
@@ -15518,7 +15523,7 @@
         <v>20</v>
       </c>
       <c r="R355" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
     </row>
     <row r="356" spans="1:18" x14ac:dyDescent="0.4">
@@ -15526,7 +15531,7 @@
         <v>1147</v>
       </c>
       <c r="B356" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C356">
         <v>891</v>
@@ -15544,7 +15549,7 @@
         <v>85</v>
       </c>
       <c r="H356" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="I356" t="s">
         <v>33</v>
@@ -15565,7 +15570,7 @@
         <v>229</v>
       </c>
       <c r="R356" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
     </row>
     <row r="357" spans="1:18" x14ac:dyDescent="0.4">
@@ -15573,7 +15578,7 @@
         <v>1170</v>
       </c>
       <c r="B357" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C357">
         <v>898</v>
@@ -15600,7 +15605,7 @@
         <v>41</v>
       </c>
       <c r="R357" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
     </row>
     <row r="358" spans="1:18" x14ac:dyDescent="0.4">
@@ -15608,7 +15613,7 @@
         <v>1173</v>
       </c>
       <c r="B358" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C358">
         <v>899</v>
@@ -15632,7 +15637,7 @@
         <v>20</v>
       </c>
       <c r="R358" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
     </row>
     <row r="359" spans="1:18" x14ac:dyDescent="0.4">
@@ -15640,7 +15645,7 @@
         <v>1186</v>
       </c>
       <c r="B359" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C359">
         <v>904</v>
@@ -15661,7 +15666,7 @@
         <v>147</v>
       </c>
       <c r="R359" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="360" spans="1:18" x14ac:dyDescent="0.4">
@@ -15669,7 +15674,7 @@
         <v>1187</v>
       </c>
       <c r="B360" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C360">
         <v>904</v>
@@ -15690,7 +15695,7 @@
         <v>33</v>
       </c>
       <c r="R360" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
     </row>
     <row r="361" spans="1:18" x14ac:dyDescent="0.4">
@@ -15698,7 +15703,7 @@
         <v>1188</v>
       </c>
       <c r="B361" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C361">
         <v>904</v>
@@ -15719,7 +15724,7 @@
         <v>20</v>
       </c>
       <c r="R361" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
     </row>
     <row r="362" spans="1:18" x14ac:dyDescent="0.4">
@@ -15727,7 +15732,7 @@
         <v>1189</v>
       </c>
       <c r="B362" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C362">
         <v>904</v>
@@ -15748,7 +15753,7 @@
         <v>20</v>
       </c>
       <c r="R362" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
     </row>
     <row r="363" spans="1:18" x14ac:dyDescent="0.4">
@@ -15756,7 +15761,7 @@
         <v>1257</v>
       </c>
       <c r="B363" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C363">
         <v>911</v>
@@ -15774,13 +15779,13 @@
         <v>268</v>
       </c>
       <c r="H363" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="I363" t="s">
         <v>33</v>
       </c>
       <c r="R363" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
     </row>
     <row r="364" spans="1:18" x14ac:dyDescent="0.4">
@@ -15788,7 +15793,7 @@
         <v>1260</v>
       </c>
       <c r="B364" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C364">
         <v>912</v>
@@ -15806,7 +15811,7 @@
         <v>268</v>
       </c>
       <c r="H364" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="I364" t="s">
         <v>20</v>
@@ -15815,7 +15820,7 @@
         <v>63</v>
       </c>
       <c r="R364" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
     </row>
     <row r="365" spans="1:18" x14ac:dyDescent="0.4">
@@ -15823,7 +15828,7 @@
         <v>1266</v>
       </c>
       <c r="B365" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C365">
         <v>913</v>
@@ -15841,7 +15846,7 @@
         <v>268</v>
       </c>
       <c r="H365" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="I365" t="s">
         <v>20</v>
@@ -15850,7 +15855,7 @@
         <v>74</v>
       </c>
       <c r="R365" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
     </row>
     <row r="366" spans="1:18" x14ac:dyDescent="0.4">
@@ -15858,7 +15863,7 @@
         <v>1267</v>
       </c>
       <c r="B366" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C366">
         <v>913</v>
@@ -15876,16 +15881,16 @@
         <v>268</v>
       </c>
       <c r="H366" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="I366" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="J366" t="s">
         <v>40</v>
       </c>
       <c r="R366" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
     </row>
     <row r="367" spans="1:18" x14ac:dyDescent="0.4">
@@ -15893,7 +15898,7 @@
         <v>1276</v>
       </c>
       <c r="B367" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C367">
         <v>915</v>
@@ -15917,7 +15922,7 @@
         <v>21</v>
       </c>
       <c r="R367" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="368" spans="1:18" x14ac:dyDescent="0.4">
@@ -15925,7 +15930,7 @@
         <v>1284</v>
       </c>
       <c r="B368" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C368">
         <v>917</v>
@@ -15946,7 +15951,7 @@
         <v>33</v>
       </c>
       <c r="R368" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
     </row>
     <row r="369" spans="1:18" x14ac:dyDescent="0.4">
@@ -15954,7 +15959,7 @@
         <v>1290</v>
       </c>
       <c r="B369" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C369">
         <v>919</v>
@@ -15972,13 +15977,13 @@
         <v>268</v>
       </c>
       <c r="H369" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="I369" t="s">
         <v>20</v>
       </c>
       <c r="R369" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
     </row>
     <row r="370" spans="1:18" x14ac:dyDescent="0.4">
@@ -15986,7 +15991,7 @@
         <v>1296</v>
       </c>
       <c r="B370" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C370">
         <v>921</v>
@@ -16007,7 +16012,7 @@
         <v>33</v>
       </c>
       <c r="R370" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
     </row>
     <row r="371" spans="1:18" x14ac:dyDescent="0.4">
@@ -16015,7 +16020,7 @@
         <v>1297</v>
       </c>
       <c r="B371" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C371">
         <v>921</v>
@@ -16033,13 +16038,13 @@
         <v>268</v>
       </c>
       <c r="H371" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="I371" t="s">
         <v>20</v>
       </c>
       <c r="R371" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
     </row>
     <row r="372" spans="1:18" x14ac:dyDescent="0.4">
@@ -16047,7 +16052,7 @@
         <v>1308</v>
       </c>
       <c r="B372" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C372">
         <v>925</v>
@@ -16068,7 +16073,7 @@
         <v>20</v>
       </c>
       <c r="R372" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
     </row>
     <row r="373" spans="1:18" x14ac:dyDescent="0.4">
@@ -16076,7 +16081,7 @@
         <v>1309</v>
       </c>
       <c r="B373" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C373">
         <v>925</v>
@@ -16097,7 +16102,7 @@
         <v>20</v>
       </c>
       <c r="R373" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="374" spans="1:18" x14ac:dyDescent="0.4">
@@ -16105,7 +16110,7 @@
         <v>1327</v>
       </c>
       <c r="B374" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="C374">
         <v>927</v>
@@ -16126,7 +16131,7 @@
         <v>33</v>
       </c>
       <c r="R374" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
     </row>
     <row r="375" spans="1:18" x14ac:dyDescent="0.4">
@@ -16134,7 +16139,7 @@
         <v>1329</v>
       </c>
       <c r="B375" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C375">
         <v>926</v>
@@ -16155,7 +16160,7 @@
         <v>20</v>
       </c>
       <c r="R375" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
     </row>
     <row r="376" spans="1:18" x14ac:dyDescent="0.4">
@@ -16163,7 +16168,7 @@
         <v>1334</v>
       </c>
       <c r="B376" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C376">
         <v>937</v>
@@ -16181,7 +16186,7 @@
         <v>268</v>
       </c>
       <c r="H376" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="I376" t="s">
         <v>33</v>
@@ -16199,7 +16204,7 @@
         <v>22</v>
       </c>
       <c r="R376" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
     </row>
     <row r="377" spans="1:18" x14ac:dyDescent="0.4">
@@ -16207,7 +16212,7 @@
         <v>1341</v>
       </c>
       <c r="B377" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C377">
         <v>929</v>
@@ -16228,7 +16233,7 @@
         <v>20</v>
       </c>
       <c r="R377" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
     </row>
     <row r="378" spans="1:18" x14ac:dyDescent="0.4">
@@ -16236,7 +16241,7 @@
         <v>1342</v>
       </c>
       <c r="B378" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C378">
         <v>929</v>
@@ -16257,7 +16262,7 @@
         <v>20</v>
       </c>
       <c r="R378" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="379" spans="1:18" x14ac:dyDescent="0.4">
@@ -16265,7 +16270,7 @@
         <v>1343</v>
       </c>
       <c r="B379" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C379">
         <v>929</v>
@@ -16292,7 +16297,7 @@
         <v>42</v>
       </c>
       <c r="R379" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
     </row>
     <row r="380" spans="1:18" x14ac:dyDescent="0.4">
@@ -16300,7 +16305,7 @@
         <v>1346</v>
       </c>
       <c r="B380" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C380">
         <v>931</v>
@@ -16321,7 +16326,7 @@
         <v>20</v>
       </c>
       <c r="R380" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
     </row>
     <row r="381" spans="1:18" x14ac:dyDescent="0.4">
@@ -16329,7 +16334,7 @@
         <v>1349</v>
       </c>
       <c r="B381" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="C381">
         <v>931</v>
@@ -16350,7 +16355,7 @@
         <v>20</v>
       </c>
       <c r="R381" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="382" spans="1:18" x14ac:dyDescent="0.4">
@@ -16358,7 +16363,7 @@
         <v>1350</v>
       </c>
       <c r="B382" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C382">
         <v>931</v>
@@ -16379,7 +16384,7 @@
         <v>20</v>
       </c>
       <c r="R382" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="383" spans="1:18" x14ac:dyDescent="0.4">
@@ -16387,7 +16392,7 @@
         <v>1351</v>
       </c>
       <c r="B383" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="C383">
         <v>931</v>
@@ -16408,7 +16413,7 @@
         <v>20</v>
       </c>
       <c r="R383" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
     </row>
     <row r="384" spans="1:18" x14ac:dyDescent="0.4">
@@ -16416,7 +16421,7 @@
         <v>1352</v>
       </c>
       <c r="B384" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C384">
         <v>931</v>
@@ -16437,7 +16442,7 @@
         <v>20</v>
       </c>
       <c r="R384" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
     </row>
     <row r="385" spans="1:18" x14ac:dyDescent="0.4">
@@ -16445,7 +16450,7 @@
         <v>1353</v>
       </c>
       <c r="B385" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C385">
         <v>931</v>
@@ -16466,7 +16471,7 @@
         <v>33</v>
       </c>
       <c r="R385" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
     </row>
     <row r="386" spans="1:18" x14ac:dyDescent="0.4">
@@ -16474,7 +16479,7 @@
         <v>1354</v>
       </c>
       <c r="B386" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C386">
         <v>931</v>
@@ -16495,7 +16500,7 @@
         <v>20</v>
       </c>
       <c r="R386" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
     </row>
     <row r="387" spans="1:18" x14ac:dyDescent="0.4">
@@ -16503,7 +16508,7 @@
         <v>1355</v>
       </c>
       <c r="B387" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C387">
         <v>931</v>
@@ -16524,7 +16529,7 @@
         <v>33</v>
       </c>
       <c r="R387" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
     </row>
     <row r="388" spans="1:18" x14ac:dyDescent="0.4">
@@ -16532,7 +16537,7 @@
         <v>1356</v>
       </c>
       <c r="B388" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="C388">
         <v>931</v>
@@ -16553,7 +16558,7 @@
         <v>20</v>
       </c>
       <c r="R388" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
     </row>
     <row r="389" spans="1:18" x14ac:dyDescent="0.4">
@@ -16561,7 +16566,7 @@
         <v>1357</v>
       </c>
       <c r="B389" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="C389">
         <v>931</v>
@@ -16582,7 +16587,7 @@
         <v>20</v>
       </c>
       <c r="R389" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
     </row>
     <row r="390" spans="1:18" x14ac:dyDescent="0.4">
@@ -16590,7 +16595,7 @@
         <v>1358</v>
       </c>
       <c r="B390" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C390">
         <v>931</v>
@@ -16614,7 +16619,7 @@
         <v>229</v>
       </c>
       <c r="R390" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="391" spans="1:18" x14ac:dyDescent="0.4">
@@ -16622,7 +16627,7 @@
         <v>1368</v>
       </c>
       <c r="B391" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C391">
         <v>937</v>
@@ -16640,13 +16645,13 @@
         <v>268</v>
       </c>
       <c r="H391" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="I391" t="s">
         <v>20</v>
       </c>
       <c r="R391" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="392" spans="1:18" x14ac:dyDescent="0.4">
@@ -16654,7 +16659,7 @@
         <v>1385</v>
       </c>
       <c r="B392" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C392">
         <v>948</v>
@@ -16675,7 +16680,7 @@
         <v>20</v>
       </c>
       <c r="R392" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
     </row>
     <row r="393" spans="1:18" x14ac:dyDescent="0.4">
@@ -16683,7 +16688,7 @@
         <v>1404</v>
       </c>
       <c r="B393" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C393">
         <v>953</v>
@@ -16701,13 +16706,13 @@
         <v>268</v>
       </c>
       <c r="H393" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="I393" t="s">
         <v>20</v>
       </c>
       <c r="R393" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
     </row>
     <row r="394" spans="1:18" x14ac:dyDescent="0.4">
@@ -16715,7 +16720,7 @@
         <v>1411</v>
       </c>
       <c r="B394" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C394">
         <v>1033</v>
@@ -16742,7 +16747,7 @@
         <v>175</v>
       </c>
       <c r="R394" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
     </row>
     <row r="395" spans="1:18" x14ac:dyDescent="0.4">
@@ -16750,7 +16755,7 @@
         <v>1497</v>
       </c>
       <c r="B395" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C395">
         <v>960</v>
@@ -16768,7 +16773,7 @@
         <v>268</v>
       </c>
       <c r="H395" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="I395" t="s">
         <v>20</v>
@@ -16786,7 +16791,7 @@
         <v>80</v>
       </c>
       <c r="R395" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
     </row>
     <row r="396" spans="1:18" x14ac:dyDescent="0.4">
@@ -16794,7 +16799,7 @@
         <v>1508</v>
       </c>
       <c r="B396" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C396">
         <v>964</v>
@@ -16815,7 +16820,7 @@
         <v>33</v>
       </c>
       <c r="R396" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
     </row>
     <row r="397" spans="1:18" x14ac:dyDescent="0.4">
@@ -16823,7 +16828,7 @@
         <v>1512</v>
       </c>
       <c r="B397" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="C397">
         <v>965</v>
@@ -16844,7 +16849,7 @@
         <v>33</v>
       </c>
       <c r="R397" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="398" spans="1:18" x14ac:dyDescent="0.4">
@@ -16852,7 +16857,7 @@
         <v>1513</v>
       </c>
       <c r="B398" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="C398">
         <v>965</v>
@@ -16873,7 +16878,7 @@
         <v>20</v>
       </c>
       <c r="R398" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
     </row>
     <row r="399" spans="1:18" x14ac:dyDescent="0.4">
@@ -16881,7 +16886,7 @@
         <v>1551</v>
       </c>
       <c r="B399" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C399">
         <v>978</v>
@@ -16908,7 +16913,7 @@
         <v>41</v>
       </c>
       <c r="R399" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
     </row>
     <row r="400" spans="1:18" x14ac:dyDescent="0.4">
@@ -16916,7 +16921,7 @@
         <v>1552</v>
       </c>
       <c r="B400" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C400">
         <v>978</v>
@@ -16937,7 +16942,7 @@
         <v>20</v>
       </c>
       <c r="R400" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="401" spans="1:18" x14ac:dyDescent="0.4">
@@ -16945,7 +16950,7 @@
         <v>1553</v>
       </c>
       <c r="B401" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C401">
         <v>978</v>
@@ -16966,7 +16971,7 @@
         <v>33</v>
       </c>
       <c r="R401" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
     </row>
     <row r="402" spans="1:18" x14ac:dyDescent="0.4">
@@ -16974,7 +16979,7 @@
         <v>1554</v>
       </c>
       <c r="B402" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C402">
         <v>978</v>
@@ -16995,7 +17000,7 @@
         <v>20</v>
       </c>
       <c r="R402" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
     </row>
     <row r="403" spans="1:18" x14ac:dyDescent="0.4">
@@ -17003,7 +17008,7 @@
         <v>1568</v>
       </c>
       <c r="B403" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C403">
         <v>981</v>
@@ -17018,13 +17023,13 @@
         <v>25</v>
       </c>
       <c r="G403" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="I403" t="s">
         <v>20</v>
       </c>
       <c r="R403" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="404" spans="1:18" x14ac:dyDescent="0.4">
@@ -17032,7 +17037,7 @@
         <v>1578</v>
       </c>
       <c r="B404" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C404">
         <v>984</v>
@@ -17056,7 +17061,7 @@
         <v>21</v>
       </c>
       <c r="R404" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
     </row>
     <row r="405" spans="1:18" x14ac:dyDescent="0.4">
@@ -17064,7 +17069,7 @@
         <v>1624</v>
       </c>
       <c r="B405" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C405">
         <v>1011</v>
@@ -17082,13 +17087,13 @@
         <v>268</v>
       </c>
       <c r="H405" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="I405" t="s">
         <v>66</v>
       </c>
       <c r="R405" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
     </row>
     <row r="406" spans="1:18" x14ac:dyDescent="0.4">
@@ -17096,7 +17101,7 @@
         <v>1635</v>
       </c>
       <c r="B406" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C406">
         <v>1024</v>
@@ -17114,13 +17119,13 @@
         <v>268</v>
       </c>
       <c r="H406" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="I406" t="s">
         <v>20</v>
       </c>
       <c r="R406" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
     </row>
     <row r="407" spans="1:18" x14ac:dyDescent="0.4">
@@ -17128,7 +17133,7 @@
         <v>1636</v>
       </c>
       <c r="B407" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C407">
         <v>1024</v>
@@ -17146,13 +17151,13 @@
         <v>268</v>
       </c>
       <c r="H407" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="I407" t="s">
         <v>20</v>
       </c>
       <c r="R407" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
     </row>
     <row r="408" spans="1:18" x14ac:dyDescent="0.4">
@@ -17160,7 +17165,7 @@
         <v>1641</v>
       </c>
       <c r="B408" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="C408">
         <v>1030</v>
@@ -17175,13 +17180,13 @@
         <v>62</v>
       </c>
       <c r="G408" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="I408" t="s">
         <v>20</v>
       </c>
       <c r="R408" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
     </row>
     <row r="409" spans="1:18" x14ac:dyDescent="0.4">
@@ -17189,7 +17194,7 @@
         <v>1678</v>
       </c>
       <c r="B409" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C409">
         <v>1053</v>
@@ -17210,7 +17215,7 @@
         <v>20</v>
       </c>
       <c r="R409" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
     </row>
     <row r="410" spans="1:18" x14ac:dyDescent="0.4">
@@ -17218,7 +17223,7 @@
         <v>1695</v>
       </c>
       <c r="B410" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="C410">
         <v>1059</v>
@@ -17236,13 +17241,13 @@
         <v>44</v>
       </c>
       <c r="H410" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="I410" t="s">
         <v>33</v>
       </c>
       <c r="R410" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
     </row>
     <row r="411" spans="1:18" x14ac:dyDescent="0.4">
@@ -17250,7 +17255,7 @@
         <v>1696</v>
       </c>
       <c r="B411" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C411">
         <v>1059</v>
@@ -17268,13 +17273,13 @@
         <v>44</v>
       </c>
       <c r="H411" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="I411" t="s">
         <v>20</v>
       </c>
       <c r="R411" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
     </row>
     <row r="412" spans="1:18" x14ac:dyDescent="0.4">
@@ -17282,7 +17287,7 @@
         <v>1702</v>
       </c>
       <c r="B412" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="C412">
         <v>1061</v>
@@ -17303,7 +17308,7 @@
         <v>33</v>
       </c>
       <c r="R412" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
     <row r="413" spans="1:18" x14ac:dyDescent="0.4">
@@ -17311,7 +17316,7 @@
         <v>1703</v>
       </c>
       <c r="B413" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="C413">
         <v>1061</v>
@@ -17332,7 +17337,7 @@
         <v>20</v>
       </c>
       <c r="R413" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
     </row>
     <row r="414" spans="1:18" x14ac:dyDescent="0.4">
@@ -17340,7 +17345,7 @@
         <v>1704</v>
       </c>
       <c r="B414" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="C414">
         <v>1061</v>
@@ -17358,13 +17363,13 @@
         <v>44</v>
       </c>
       <c r="H414" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="I414" t="s">
         <v>33</v>
       </c>
       <c r="R414" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
     </row>
     <row r="415" spans="1:18" x14ac:dyDescent="0.4">
@@ -17372,7 +17377,7 @@
         <v>1713</v>
       </c>
       <c r="B415" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="C415">
         <v>1062</v>
@@ -17390,13 +17395,13 @@
         <v>44</v>
       </c>
       <c r="H415" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="I415" t="s">
         <v>20</v>
       </c>
       <c r="R415" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
     </row>
     <row r="416" spans="1:18" x14ac:dyDescent="0.4">
@@ -17404,7 +17409,7 @@
         <v>1717</v>
       </c>
       <c r="B416" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="C416">
         <v>1062</v>
@@ -17422,13 +17427,13 @@
         <v>44</v>
       </c>
       <c r="H416" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="I416" t="s">
         <v>33</v>
       </c>
       <c r="R416" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
     </row>
     <row r="417" spans="1:18" x14ac:dyDescent="0.4">
@@ -17436,7 +17441,7 @@
         <v>1718</v>
       </c>
       <c r="B417" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="C417">
         <v>1062</v>
@@ -17454,13 +17459,13 @@
         <v>44</v>
       </c>
       <c r="H417" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="I417" t="s">
         <v>20</v>
       </c>
       <c r="R417" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
     </row>
     <row r="418" spans="1:18" x14ac:dyDescent="0.4">
@@ -17468,7 +17473,7 @@
         <v>1737</v>
       </c>
       <c r="B418" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C418">
         <v>1065</v>
@@ -17486,13 +17491,13 @@
         <v>44</v>
       </c>
       <c r="H418" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="I418" t="s">
         <v>20</v>
       </c>
       <c r="R418" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
     </row>
     <row r="419" spans="1:18" x14ac:dyDescent="0.4">
@@ -17500,7 +17505,7 @@
         <v>1738</v>
       </c>
       <c r="B419" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="C419">
         <v>1065</v>
@@ -17518,13 +17523,13 @@
         <v>44</v>
       </c>
       <c r="H419" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="I419" t="s">
         <v>20</v>
       </c>
       <c r="R419" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
     </row>
     <row r="420" spans="1:18" x14ac:dyDescent="0.4">
@@ -17532,7 +17537,7 @@
         <v>1739</v>
       </c>
       <c r="B420" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C420">
         <v>1065</v>
@@ -17550,13 +17555,13 @@
         <v>44</v>
       </c>
       <c r="H420" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="I420" t="s">
         <v>20</v>
       </c>
       <c r="R420" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
     </row>
     <row r="421" spans="1:18" x14ac:dyDescent="0.4">
@@ -17564,7 +17569,7 @@
         <v>1740</v>
       </c>
       <c r="B421" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C421">
         <v>1065</v>
@@ -17582,13 +17587,13 @@
         <v>44</v>
       </c>
       <c r="H421" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="I421" t="s">
         <v>33</v>
       </c>
       <c r="R421" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
     </row>
     <row r="422" spans="1:18" x14ac:dyDescent="0.4">
@@ -17596,7 +17601,7 @@
         <v>1742</v>
       </c>
       <c r="B422" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="C422">
         <v>1066</v>
@@ -17614,13 +17619,13 @@
         <v>85</v>
       </c>
       <c r="H422" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="I422" t="s">
         <v>20</v>
       </c>
       <c r="R422" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
     </row>
     <row r="423" spans="1:18" x14ac:dyDescent="0.4">
@@ -17628,7 +17633,7 @@
         <v>1771</v>
       </c>
       <c r="B423" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="C423">
         <v>1080</v>
@@ -17655,7 +17660,7 @@
         <v>28</v>
       </c>
       <c r="R423" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
     </row>
     <row r="424" spans="1:18" x14ac:dyDescent="0.4">
@@ -17663,7 +17668,7 @@
         <v>1792</v>
       </c>
       <c r="B424" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="C424">
         <v>1095</v>
@@ -17681,7 +17686,7 @@
         <v>44</v>
       </c>
       <c r="H424" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="I424" t="s">
         <v>33</v>
@@ -17690,7 +17695,7 @@
         <v>80</v>
       </c>
       <c r="R424" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
     </row>
     <row r="425" spans="1:18" x14ac:dyDescent="0.4">
@@ -17698,7 +17703,7 @@
         <v>1818</v>
       </c>
       <c r="B425" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="C425">
         <v>1099</v>
@@ -17725,7 +17730,7 @@
         <v>63</v>
       </c>
       <c r="R425" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
     </row>
     <row r="426" spans="1:18" x14ac:dyDescent="0.4">
@@ -17733,7 +17738,7 @@
         <v>1822</v>
       </c>
       <c r="B426" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="C426">
         <v>1154</v>
@@ -17760,7 +17765,7 @@
         <v>63</v>
       </c>
       <c r="R426" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
     </row>
   </sheetData>

--- a/data/profile2.xlsx
+++ b/data/profile2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/94468aa6da851130/Desktop/reto/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="454" documentId="8_{1E7C5D3D-50BB-4B39-8D4F-14058A714382}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{57A3F383-8FCB-4CC5-8C11-BB6D819F97C1}"/>
+  <xr:revisionPtr revIDLastSave="462" documentId="8_{1E7C5D3D-50BB-4B39-8D4F-14058A714382}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E2036509-850D-4387-8298-69CA10A4DCEF}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="3510" yWindow="3510" windowWidth="17820" windowHeight="8460" xr2:uid="{298304A4-FB78-45B5-B8F6-A597285BA23E}"/>
+    <workbookView xWindow="3510" yWindow="1650" windowWidth="24690" windowHeight="13890" xr2:uid="{298304A4-FB78-45B5-B8F6-A597285BA23E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -4120,7 +4120,7 @@
         <v>33</v>
       </c>
       <c r="R4" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.4">
@@ -4158,7 +4158,7 @@
         <v>21</v>
       </c>
       <c r="R5" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.4">
@@ -4514,7 +4514,7 @@
         <v>20</v>
       </c>
       <c r="R15" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.4">
@@ -4584,7 +4584,7 @@
         <v>20</v>
       </c>
       <c r="R17" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.4">
